--- a/Result/checksun_type/數位內容.xlsx
+++ b/Result/checksun_type/數位內容.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>149.38</t>
+          <t>145.88</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-11.17</v>
+        <v>-15.74</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,32 +1182,32 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,67 +1450,67 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.61</t>
+          <t>-104.37</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>148.46</t>
+          <t>149.38</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-10.17221628922797</t>
+          <t>-10.32524633056233</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-17.52</v>
+        <v>-11.17</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,32 +1613,32 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1886,64 +1886,64 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>19.03</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>19.05</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.82</t>
+          <t>-104.61</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1971,31 +1971,31 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>149.84</t>
+          <t>148.46</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-8.837099205753413</t>
+          <t>-10.17221628922797</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-13.1</v>
+        <v>-17.52</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2044,17 +2044,17 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2312,37 +2312,37 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -2357,17 +2357,17 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-19.28</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,22 +2392,22 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -2417,16 +2417,16 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-8.061684293016393</t>
+          <t>-8.837099205753413</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-6.33</v>
+        <v>-13.1</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2743,62 +2743,62 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>58.31</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-43.17</t>
+          <t>-19.28</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.62</t>
+          <t>-104.85</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>111.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>148.52</t>
+          <t>149.84</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-8.376720189178144</t>
+          <t>-8.061684293016393</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-5.75</v>
+        <v>-6.33</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,22 +2906,22 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3174,69 +3174,69 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>58.31</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>18.38</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-43.17</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>18.32</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>19.09</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-72.00</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-104.62</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>123.9</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>146.46</t>
+          <t>148.52</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-8.854520802377994</t>
+          <t>-8.376720189178144</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-7.07</v>
+        <v>-5.75</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,32 +3337,32 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3605,42 +3605,42 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.32</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -3650,22 +3650,22 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-115.09</t>
+          <t>-72.00</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.38</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>183.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>122.6</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>128.1</t>
+          <t>123.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>145.46</t>
+          <t>146.46</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-9.17864632394204</t>
+          <t>-8.854520802377994</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-13.85</v>
+        <v>-7.07</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,32 +3768,32 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4036,27 +4036,27 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4066,37 +4066,37 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-180.42</t>
+          <t>-115.09</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.40</t>
+          <t>-103.38</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -4131,26 +4131,26 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>126.6</t>
+          <t>128.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.46</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-8.328919899724902</t>
+          <t>-9.17864632394204</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-9.76</v>
+        <v>-13.85</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,27 +4199,27 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4467,67 +4467,67 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-365.46</t>
+          <t>-180.42</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.32</t>
+          <t>-102.40</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>152.4</t>
+          <t>122.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>126.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>144.94</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8.069111351122272</t>
+          <t>-8.328919899724902</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-4.52</v>
+        <v>-9.76</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,32 +4630,32 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.57</t>
+          <t>19.34</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4903,180 +4903,180 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>-0.36</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>18.51</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>19.13</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>19.07</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>19.14</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-365.46</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-101.32</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>1760.801928783383</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>152.4</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>127.7</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>144.94</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-8.069111351122272</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>-4.52</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>-5.28</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>正能量智能</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>正能量智能</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>運動休閒</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
           <t>0.47</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>-0.38</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>18.67</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>19.18</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>19.17</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-3273.41</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-100.11</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>1763.369242199109</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>96.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>127.4</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>111.2</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>144.72</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-8.713550965896541</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-11.57</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-3.17</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>正能量智能</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>正能量智能</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>運動休閒</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>14.57</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5374,22 +5374,22 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.19</t>
+          <t>19.17</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-361.29</t>
+          <t>-3273.41</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-99.18</t>
+          <t>-100.11</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>125.6</t>
+          <t>127.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>107.6</t>
+          <t>111.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>145.86</t>
+          <t>144.72</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8.194977207752418</t>
+          <t>-8.713550965896541</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-9.529999999999999</v>
+        <v>-11.57</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,42 +5619,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>16934.062</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>16854.118</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>50.8</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.07</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>946394875.2</t>
+          <t>1030169557.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>2163437979.1</t>
+          <t>1957468999.34</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>61794246.37</v>
+        <v>50764557.16</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5923,32 +5923,32 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>52365.835</t>
+          <t>16854.118</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6196,62 +6196,62 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>54.85</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-133.56</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>955349345.2</t>
+          <t>946394875.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>721647627.7</t>
+          <t>771003853.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>2402549153.18</t>
+          <t>2163437979.1</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>233701717</t>
+          <t>175391021</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-144174153.2400175</t>
+          <t>-112486707.1454632</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>76961261.38</v>
+        <v>61794246.37</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6354,17 +6354,17 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,17 +6434,17 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7426.262</t>
+          <t>52365.835</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-24.74</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>50.98</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>59.29</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>54.73</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-136.12</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>381782819.0</t>
+          <t>2715531091.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>505140710.2</t>
+          <t>955349345.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>501963719.2</t>
+          <t>721647627.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>2548936714.28</t>
+          <t>2402549153.18</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3176991</t>
+          <t>233701717</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-184380592.2611023</t>
+          <t>-144174153.2400175</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-102649650.64</v>
+        <v>76961261.38</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6785,32 +6785,32 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="CD15" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6580.167</t>
+          <t>7426.262</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-30.37</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>50.98</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>59.59</t>
+          <t>59.29</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-136.69</t>
+          <t>-136.12</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>313260581.0</t>
+          <t>381782819.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>531114807.2</t>
+          <t>505140710.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>511080645.4</t>
+          <t>501963719.2</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>2772797348.26</t>
+          <t>2548936714.28</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>20034161</t>
+          <t>3176991</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-199240763.4657515</t>
+          <t>-184380592.2611023</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-105526151.13</v>
+        <v>-102649650.64</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>17.21</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7216,32 +7216,32 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>9726.752</t>
+          <t>6580.167</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-29.93</t>
+          <t>-30.37</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,62 +7489,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-14.3</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>59.59</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-136.15</t>
+          <t>-136.69</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>458810419.0</t>
+          <t>313260581.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>583628887.2</t>
+          <t>531114807.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>529295603.5</t>
+          <t>511080645.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>2895834496.86</t>
+          <t>2772797348.26</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>54333283</t>
+          <t>20034161</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-216279783.8905731</t>
+          <t>-199240763.4657515</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-98524978.08</v>
+        <v>-105526151.13</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>17.21</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7647,22 +7647,22 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18985.299</t>
+          <t>9726.752</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-29.63</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7920,62 +7920,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-13.94</t>
+          <t>-14.3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>51.78</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>54.31</t>
+          <t>54.43</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-135.73</t>
+          <t>-136.15</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>907361816.0</t>
+          <t>458810419.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>595612832.4</t>
+          <t>583628887.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>525692219.6</t>
+          <t>529295603.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2953848981.62</t>
+          <t>2895834496.86</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>69920612</t>
+          <t>54333283</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-237689748.5834216</t>
+          <t>-216279783.8905731</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-100599178.58</v>
+        <v>-98524978.08</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.96</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8078,32 +8078,32 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
+          <t>46.8</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
           <t>47.3</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>47.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9234.129</t>
+          <t>18985.299</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-29.63</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,17 +8336,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-13.94</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>50.58</t>
+          <t>49.98</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>52.26</t>
+          <t>51.78</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>60.42</t>
+          <t>60.17</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>54.19</t>
+          <t>54.31</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-135.56</t>
+          <t>-135.73</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>464487916.0</t>
+          <t>907361816.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>487945910.2</t>
+          <t>595612832.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>469310663.0</t>
+          <t>525692219.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>3055293723.54</t>
+          <t>2953848981.62</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>18635247</t>
+          <t>69920612</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-262615306.766223</t>
+          <t>-237689748.5834216</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-148028572.59</v>
+        <v>-100599178.58</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8509,32 +8509,32 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10271.075</t>
+          <t>9234.129</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-25.48</t>
+          <t>-24.89</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-12.86</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.58</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>52.26</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>60.63</t>
+          <t>60.42</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>54.03</t>
+          <t>54.19</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-135.86</t>
+          <t>-135.56</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>511653304.0</t>
+          <t>464487916.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>498786728.2</t>
+          <t>487945910.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>463094155.0</t>
+          <t>469310663.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>3237534067.52</t>
+          <t>3055293723.54</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>35692573</t>
+          <t>18635247</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-283449258.4345579</t>
+          <t>-262615306.766223</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-163047340.02</v>
+        <v>-148028572.59</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8940,17 +8940,17 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>11439.749</t>
+          <t>10271.075</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>7.71</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-26.37</t>
+          <t>-25.48</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,72 +9198,72 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-12.86</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>12.22</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>50.72000000000001</t>
+          <t>50.52</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>52.84</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>60.82</t>
+          <t>60.63</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>53.86</t>
+          <t>54.03</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-135.87</t>
+          <t>-135.86</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>575830981.0</t>
+          <t>511653304.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>491046483.6</t>
+          <t>498786728.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>466191474.3</t>
+          <t>463094155.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>3329174084.28</t>
+          <t>3237534067.52</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>24855009</t>
+          <t>35692573</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-305340516.3289255</t>
+          <t>-283449258.4345579</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-183733037.19</v>
+        <v>-163047340.02</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10045.651</t>
+          <t>11439.749</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-26.37</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,17 +9629,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-11.35</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>51.23999999999999</t>
+          <t>50.72000000000001</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>60.92</t>
+          <t>60.82</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>53.71</t>
+          <t>53.86</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-135.67</t>
+          <t>-135.87</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>518730145.0</t>
+          <t>575830981.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>474962319.8</t>
+          <t>491046483.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>458641312.8</t>
+          <t>466191474.3</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>3509950642.14</t>
+          <t>3329174084.28</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>16321007</t>
+          <t>24855009</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-327450967.0807714</t>
+          <t>-305340516.3289255</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-213598318.66</v>
+        <v>-183733037.19</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9802,22 +9802,22 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7274.055</t>
+          <t>10045.651</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-25.19</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-10.81</t>
+          <t>-11.35</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>51.34</t>
+          <t>51.23999999999999</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>54.42</t>
+          <t>54.01</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>60.92</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>53.54</t>
+          <t>53.71</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-7.60</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-135.52</t>
+          <t>-135.67</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>369027205.0</t>
+          <t>518730145.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>455771606.8</t>
+          <t>474962319.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>478360854.2</t>
+          <t>458641312.8</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>3627840142.66</t>
+          <t>3509950642.14</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-22589247</t>
+          <t>16321007</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-348151448.6125913</t>
+          <t>-327450967.0807714</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-242516548.36</v>
+        <v>-213598318.66</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10233,22 +10233,22 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/數位內容.xlsx
+++ b/Result/checksun_type/數位內容.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1014,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>145.88</t>
+          <t>147.56</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-15.74</v>
+        <v>-5.5</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,32 +1445,32 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>149.38</t>
+          <t>145.88</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-11.17</v>
+        <v>-15.74</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,72 +1876,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.61</t>
+          <t>-104.37</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>148.46</t>
+          <t>149.38</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-10.17221628922797</t>
+          <t>-10.32524633056233</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-17.52</v>
+        <v>-11.17</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-9.54</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,64 +2317,64 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>19.03</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>19.05</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.82</t>
+          <t>-104.61</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -2402,31 +2402,31 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>149.84</t>
+          <t>148.46</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-8.837099205753413</t>
+          <t>-10.17221628922797</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-13.1</v>
+        <v>-17.52</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-9.54</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,42 +2738,42 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2788,17 +2788,17 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-19.28</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,22 +2823,22 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -2848,16 +2848,16 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-8.061684293016393</t>
+          <t>-8.837099205753413</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-6.33</v>
+        <v>-13.1</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,67 +3169,67 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>58.31</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-43.17</t>
+          <t>-19.28</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.62</t>
+          <t>-104.85</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>111.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>148.52</t>
+          <t>149.84</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-8.376720189178144</t>
+          <t>-8.061684293016393</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-5.75</v>
+        <v>-6.33</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,126 +3600,126 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>73.68</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>58.31</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>-3.24</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>18.38</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-43.17</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-104.62</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>1758.628888888889</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>128.7</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>148.52</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>63.16</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>43.43</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-3.64</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>18.32</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>19.09</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-72.00</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-104.12</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>1760.801928783383</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>183.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>122.2</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>123.9</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>146.46</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-8.854520802377994</t>
+          <t>-8.376720189178144</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-7.07</v>
+        <v>-5.75</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,47 +4031,47 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.32</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4081,22 +4081,22 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-115.09</t>
+          <t>-72.00</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.38</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>183.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>122.6</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>128.1</t>
+          <t>123.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>145.46</t>
+          <t>146.46</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-9.17864632394204</t>
+          <t>-8.854520802377994</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-13.85</v>
+        <v>-7.07</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,17 +4214,17 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,32 +4462,32 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4497,37 +4497,37 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-180.42</t>
+          <t>-115.09</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.40</t>
+          <t>-103.38</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -4562,26 +4562,26 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>126.6</t>
+          <t>128.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.46</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8.328919899724902</t>
+          <t>-9.17864632394204</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-9.76</v>
+        <v>-13.85</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,72 +4893,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-365.46</t>
+          <t>-180.42</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.32</t>
+          <t>-102.40</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>152.4</t>
+          <t>122.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>126.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>144.94</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-8.069111351122272</t>
+          <t>-8.328919899724902</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-4.52</v>
+        <v>-9.76</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14.57</t>
+          <t>19.34</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>19.13</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>19.14</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-3273.41</t>
+          <t>-365.46</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-100.11</t>
+          <t>-101.32</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>127.4</t>
+          <t>152.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>111.2</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>144.72</t>
+          <t>144.94</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8.713550965896541</t>
+          <t>-8.069111351122272</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-11.57</v>
+        <v>-4.52</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,67 +5750,67 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>58.07</t>
+          <t>57.56</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>1030169557.8</t>
+          <t>1149525583.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>1957468999.34</t>
+          <t>1776903570.96</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>50764557.16</v>
+        <v>44201426.71</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,17 +5938,17 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6008,17 +6008,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16854.118</t>
+          <t>16934.062</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.07</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>946394875.2</t>
+          <t>1030169557.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>2163437979.1</t>
+          <t>1957468999.34</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>61794246.37</v>
+        <v>50764557.16</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,17 +6369,17 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>52365.835</t>
+          <t>16854.118</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,62 +6627,62 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>54.85</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-133.56</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>955349345.2</t>
+          <t>946394875.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>721647627.7</t>
+          <t>771003853.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>2402549153.18</t>
+          <t>2163437979.1</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>233701717</t>
+          <t>175391021</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-144174153.2400175</t>
+          <t>-112486707.1454632</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>76961261.38</v>
+        <v>61794246.37</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7426.262</t>
+          <t>52365.835</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-24.74</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>50.98</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>59.29</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>54.73</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-136.12</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>381782819.0</t>
+          <t>2715531091.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>505140710.2</t>
+          <t>955349345.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>501963719.2</t>
+          <t>721647627.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>2548936714.28</t>
+          <t>2402549153.18</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>3176991</t>
+          <t>233701717</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-184380592.2611023</t>
+          <t>-144174153.2400175</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-102649650.64</v>
+        <v>76961261.38</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,17 +7231,17 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="CD16" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6580.167</t>
+          <t>7426.262</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-30.37</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>50.98</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>59.59</t>
+          <t>59.29</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-136.69</t>
+          <t>-136.12</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>313260581.0</t>
+          <t>381782819.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>531114807.2</t>
+          <t>505140710.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>511080645.4</t>
+          <t>501963719.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>2772797348.26</t>
+          <t>2548936714.28</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>20034161</t>
+          <t>3176991</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-199240763.4657515</t>
+          <t>-184380592.2611023</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-105526151.13</v>
+        <v>-102649650.64</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>17.21</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,17 +7662,17 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9726.752</t>
+          <t>6580.167</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-29.93</t>
+          <t>-30.37</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7920,62 +7920,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-14.3</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>59.59</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-136.15</t>
+          <t>-136.69</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>458810419.0</t>
+          <t>313260581.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>583628887.2</t>
+          <t>531114807.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>529295603.5</t>
+          <t>511080645.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2895834496.86</t>
+          <t>2772797348.26</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>54333283</t>
+          <t>20034161</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-216279783.8905731</t>
+          <t>-199240763.4657515</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-98524978.08</v>
+        <v>-105526151.13</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>17.21</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18985.299</t>
+          <t>9726.752</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-29.63</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8351,62 +8351,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-13.94</t>
+          <t>-14.3</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>51.78</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>54.31</t>
+          <t>54.43</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-135.73</t>
+          <t>-136.15</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>907361816.0</t>
+          <t>458810419.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>595612832.4</t>
+          <t>583628887.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>525692219.6</t>
+          <t>529295603.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2953848981.62</t>
+          <t>2895834496.86</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>69920612</t>
+          <t>54333283</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-237689748.5834216</t>
+          <t>-216279783.8905731</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-100599178.58</v>
+        <v>-98524978.08</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.96</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,17 +8524,17 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
+          <t>46.8</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
           <t>47.3</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>47.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9234.129</t>
+          <t>18985.299</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-29.63</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,17 +8767,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8787,57 +8787,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-13.94</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>50.58</t>
+          <t>49.98</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>52.26</t>
+          <t>51.78</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>60.42</t>
+          <t>60.17</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>54.19</t>
+          <t>54.31</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-135.56</t>
+          <t>-135.73</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>464487916.0</t>
+          <t>907361816.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>487945910.2</t>
+          <t>595612832.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>469310663.0</t>
+          <t>525692219.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>3055293723.54</t>
+          <t>2953848981.62</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>18635247</t>
+          <t>69920612</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-262615306.766223</t>
+          <t>-237689748.5834216</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-148028572.59</v>
+        <v>-100599178.58</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,17 +8955,17 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10271.075</t>
+          <t>9234.129</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-25.48</t>
+          <t>-24.89</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-12.86</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.58</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>52.26</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>60.63</t>
+          <t>60.42</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>54.03</t>
+          <t>54.19</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-135.86</t>
+          <t>-135.56</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>511653304.0</t>
+          <t>464487916.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>498786728.2</t>
+          <t>487945910.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>463094155.0</t>
+          <t>469310663.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>3237534067.52</t>
+          <t>3055293723.54</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>35692573</t>
+          <t>18635247</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-283449258.4345579</t>
+          <t>-262615306.766223</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-163047340.02</v>
+        <v>-148028572.59</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11439.749</t>
+          <t>10271.075</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>7.71</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-26.37</t>
+          <t>-25.48</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,72 +9629,72 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-12.86</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>12.22</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>50.72000000000001</t>
+          <t>50.52</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>52.84</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>60.82</t>
+          <t>60.63</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>53.86</t>
+          <t>54.03</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-135.87</t>
+          <t>-135.86</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>575830981.0</t>
+          <t>511653304.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>491046483.6</t>
+          <t>498786728.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>466191474.3</t>
+          <t>463094155.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>3329174084.28</t>
+          <t>3237534067.52</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>24855009</t>
+          <t>35692573</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-305340516.3289255</t>
+          <t>-283449258.4345579</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-183733037.19</v>
+        <v>-163047340.02</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10045.651</t>
+          <t>11439.749</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-26.37</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,17 +10060,17 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -10080,57 +10080,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-11.35</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>51.23999999999999</t>
+          <t>50.72000000000001</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>60.92</t>
+          <t>60.82</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>53.71</t>
+          <t>53.86</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-135.67</t>
+          <t>-135.87</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>518730145.0</t>
+          <t>575830981.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>474962319.8</t>
+          <t>491046483.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>458641312.8</t>
+          <t>466191474.3</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>3509950642.14</t>
+          <t>3329174084.28</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>16321007</t>
+          <t>24855009</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-327450967.0807714</t>
+          <t>-305340516.3289255</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-213598318.66</v>
+        <v>-183733037.19</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/數位內容.xlsx
+++ b/Result/checksun_type/數位內容.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>18.99</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>19.01</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>19.02</t>
-        </is>
-      </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>147.56</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-5.5</v>
+        <v>-7.5</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>145.88</t>
+          <t>147.56</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-15.74</v>
+        <v>-5.5</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,37 +1871,37 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>149.38</t>
+          <t>145.88</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-11.17</v>
+        <v>-15.74</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-9.54</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.61</t>
+          <t>-104.37</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>148.46</t>
+          <t>149.38</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-10.17221628922797</t>
+          <t>-10.32524633056233</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-17.52</v>
+        <v>-11.17</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-9.54</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,64 +2748,64 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>19.03</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>19.05</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.82</t>
+          <t>-104.61</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2833,31 +2833,31 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>149.84</t>
+          <t>148.46</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-8.837099205753413</t>
+          <t>-10.17221628922797</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-13.1</v>
+        <v>-17.52</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,47 +3164,47 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -3219,17 +3219,17 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-19.28</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,22 +3254,22 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -3279,16 +3279,16 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-8.061684293016393</t>
+          <t>-8.837099205753413</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-6.33</v>
+        <v>-13.1</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,72 +3595,72 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>58.31</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-43.17</t>
+          <t>-19.28</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.62</t>
+          <t>-104.85</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>111.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>148.52</t>
+          <t>149.84</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-8.376720189178144</t>
+          <t>-8.061684293016393</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-5.75</v>
+        <v>-6.33</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,79 +4026,79 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>58.31</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>18.38</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-43.17</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>18.32</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>19.09</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-72.00</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-104.62</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>123.9</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>146.46</t>
+          <t>148.52</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-8.854520802377994</t>
+          <t>-8.376720189178144</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-7.07</v>
+        <v>-5.75</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,17 +4214,17 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,52 +4457,52 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.32</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4512,22 +4512,22 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-115.09</t>
+          <t>-72.00</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.38</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>183.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>122.6</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>128.1</t>
+          <t>123.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>145.46</t>
+          <t>146.46</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-9.17864632394204</t>
+          <t>-8.854520802377994</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-13.85</v>
+        <v>-7.07</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,37 +4888,37 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4928,37 +4928,37 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-180.42</t>
+          <t>-115.09</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.40</t>
+          <t>-103.38</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -4993,26 +4993,26 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>126.6</t>
+          <t>128.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.46</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-8.328919899724902</t>
+          <t>-9.17864632394204</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-9.76</v>
+        <v>-13.85</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-365.46</t>
+          <t>-180.42</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.32</t>
+          <t>-102.40</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>152.4</t>
+          <t>122.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>126.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>144.94</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8.069111351122272</t>
+          <t>-8.328919899724902</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-4.52</v>
+        <v>-9.76</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>50.38</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>57.56</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>1149525583.8</t>
+          <t>1199384865.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>1776903570.96</t>
+          <t>1647059956.98</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>44201426.71</v>
+        <v>17580088.43</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,67 +6181,67 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>58.07</t>
+          <t>57.56</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>1030169557.8</t>
+          <t>1149525583.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>1957468999.34</t>
+          <t>1776903570.96</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>50764557.16</v>
+        <v>44201426.71</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,17 +6369,17 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6439,17 +6439,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>16854.118</t>
+          <t>16934.062</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.07</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>946394875.2</t>
+          <t>1030169557.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>2163437979.1</t>
+          <t>1957468999.34</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>61794246.37</v>
+        <v>50764557.16</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,17 +6800,17 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>52365.835</t>
+          <t>16854.118</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,62 +7058,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>54.85</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-133.56</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>955349345.2</t>
+          <t>946394875.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>721647627.7</t>
+          <t>771003853.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>2402549153.18</t>
+          <t>2163437979.1</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>233701717</t>
+          <t>175391021</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-144174153.2400175</t>
+          <t>-112486707.1454632</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>76961261.38</v>
+        <v>61794246.37</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,17 +7296,17 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7426.262</t>
+          <t>52365.835</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-24.74</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>50.98</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>59.29</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>54.73</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-136.12</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>381782819.0</t>
+          <t>2715531091.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>505140710.2</t>
+          <t>955349345.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>501963719.2</t>
+          <t>721647627.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>2548936714.28</t>
+          <t>2402549153.18</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>3176991</t>
+          <t>233701717</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-184380592.2611023</t>
+          <t>-144174153.2400175</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-102649650.64</v>
+        <v>76961261.38</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,17 +7662,17 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="CD17" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6580.167</t>
+          <t>7426.262</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-30.37</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>50.98</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>59.59</t>
+          <t>59.29</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-136.69</t>
+          <t>-136.12</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>313260581.0</t>
+          <t>381782819.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>531114807.2</t>
+          <t>505140710.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>511080645.4</t>
+          <t>501963719.2</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2772797348.26</t>
+          <t>2548936714.28</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>20034161</t>
+          <t>3176991</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-199240763.4657515</t>
+          <t>-184380592.2611023</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-105526151.13</v>
+        <v>-102649650.64</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>17.21</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,17 +8093,17 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9726.752</t>
+          <t>6580.167</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-29.93</t>
+          <t>-30.37</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8351,62 +8351,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-14.3</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>59.59</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-136.15</t>
+          <t>-136.69</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>458810419.0</t>
+          <t>313260581.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>583628887.2</t>
+          <t>531114807.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>529295603.5</t>
+          <t>511080645.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2895834496.86</t>
+          <t>2772797348.26</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>54333283</t>
+          <t>20034161</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-216279783.8905731</t>
+          <t>-199240763.4657515</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-98524978.08</v>
+        <v>-105526151.13</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>17.21</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>18985.299</t>
+          <t>9726.752</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-29.63</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8782,62 +8782,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-13.94</t>
+          <t>-14.3</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>51.78</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>54.31</t>
+          <t>54.43</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-135.73</t>
+          <t>-136.15</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>907361816.0</t>
+          <t>458810419.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>595612832.4</t>
+          <t>583628887.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>525692219.6</t>
+          <t>529295603.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>2953848981.62</t>
+          <t>2895834496.86</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>69920612</t>
+          <t>54333283</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-237689748.5834216</t>
+          <t>-216279783.8905731</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-100599178.58</v>
+        <v>-98524978.08</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.96</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,17 +8955,17 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
+          <t>46.8</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>47.3</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>47.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9234.129</t>
+          <t>18985.299</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-29.63</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,17 +9198,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9218,57 +9218,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-13.94</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>50.58</t>
+          <t>49.98</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>52.26</t>
+          <t>51.78</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>60.42</t>
+          <t>60.17</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>54.19</t>
+          <t>54.31</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-135.56</t>
+          <t>-135.73</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>464487916.0</t>
+          <t>907361816.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>487945910.2</t>
+          <t>595612832.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>469310663.0</t>
+          <t>525692219.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>3055293723.54</t>
+          <t>2953848981.62</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>18635247</t>
+          <t>69920612</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-262615306.766223</t>
+          <t>-237689748.5834216</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-148028572.59</v>
+        <v>-100599178.58</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,17 +9386,17 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10271.075</t>
+          <t>9234.129</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-25.48</t>
+          <t>-24.89</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-12.86</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.58</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>52.26</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>60.63</t>
+          <t>60.42</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>54.03</t>
+          <t>54.19</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-135.86</t>
+          <t>-135.56</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>511653304.0</t>
+          <t>464487916.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>498786728.2</t>
+          <t>487945910.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>463094155.0</t>
+          <t>469310663.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>3237534067.52</t>
+          <t>3055293723.54</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>35692573</t>
+          <t>18635247</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-283449258.4345579</t>
+          <t>-262615306.766223</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-163047340.02</v>
+        <v>-148028572.59</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>11439.749</t>
+          <t>10271.075</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>7.71</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-26.37</t>
+          <t>-25.48</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,72 +10060,72 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-12.86</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>12.22</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>50.72000000000001</t>
+          <t>50.52</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>52.84</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>60.82</t>
+          <t>60.63</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>53.86</t>
+          <t>54.03</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-135.87</t>
+          <t>-135.86</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>575830981.0</t>
+          <t>511653304.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>491046483.6</t>
+          <t>498786728.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>466191474.3</t>
+          <t>463094155.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>3329174084.28</t>
+          <t>3237534067.52</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>24855009</t>
+          <t>35692573</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-305340516.3289255</t>
+          <t>-283449258.4345579</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-183733037.19</v>
+        <v>-163047340.02</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/數位內容.xlsx
+++ b/Result/checksun_type/數位內容.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1014,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>18.99</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>112.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>149.36</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-7.5</v>
+        <v>-4.58</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,72 +1445,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>18.99</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
           <t>19.01</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>19.02</t>
-        </is>
-      </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>147.56</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-5.5</v>
+        <v>-7.5</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,72 +1876,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>145.88</t>
+          <t>147.56</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-15.74</v>
+        <v>-5.5</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,32 +2307,32 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>149.38</t>
+          <t>145.88</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-11.17</v>
+        <v>-15.74</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,72 +2738,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.61</t>
+          <t>-104.37</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>148.46</t>
+          <t>149.38</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-10.17221628922797</t>
+          <t>-10.32524633056233</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-17.52</v>
+        <v>-11.17</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-9.54</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,64 +3179,64 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>19.03</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>19.05</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.82</t>
+          <t>-104.61</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -3264,31 +3264,31 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>149.84</t>
+          <t>148.46</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-8.837099205753413</t>
+          <t>-10.17221628922797</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-13.1</v>
+        <v>-17.52</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-9.54</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,42 +3600,42 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -3650,17 +3650,17 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-19.28</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,22 +3685,22 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -3710,16 +3710,16 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-8.061684293016393</t>
+          <t>-8.837099205753413</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-6.33</v>
+        <v>-13.1</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,67 +4031,67 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>58.31</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-43.17</t>
+          <t>-19.28</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.62</t>
+          <t>-104.85</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>111.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>148.52</t>
+          <t>149.84</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-8.376720189178144</t>
+          <t>-8.061684293016393</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-5.75</v>
+        <v>-6.33</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,74 +4462,74 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>58.31</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>18.38</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-43.17</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>18.32</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>19.09</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-72.00</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-104.62</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>123.9</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>146.46</t>
+          <t>148.52</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8.854520802377994</t>
+          <t>-8.376720189178144</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-7.07</v>
+        <v>-5.75</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,47 +4893,47 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.32</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -4943,22 +4943,22 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-115.09</t>
+          <t>-72.00</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.38</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>183.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>122.6</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>128.1</t>
+          <t>123.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>145.46</t>
+          <t>146.46</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-9.17864632394204</t>
+          <t>-8.854520802377994</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-13.85</v>
+        <v>-7.07</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,32 +5324,32 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5359,37 +5359,37 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-180.42</t>
+          <t>-115.09</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.40</t>
+          <t>-103.38</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -5424,26 +5424,26 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>126.6</t>
+          <t>128.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.46</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8.328919899724902</t>
+          <t>-9.17864632394204</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-9.76</v>
+        <v>-13.85</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>50.18</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>1199384865.4</t>
+          <t>751503060.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>1647059956.98</t>
+          <t>1565117969.24</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>17580088.43</v>
+        <v>-13116137.58</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>50.38</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>57.56</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>1149525583.8</t>
+          <t>1199384865.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>1776903570.96</t>
+          <t>1647059956.98</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>44201426.71</v>
+        <v>17580088.43</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,67 +6612,67 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>58.07</t>
+          <t>57.56</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>1030169557.8</t>
+          <t>1149525583.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>1957468999.34</t>
+          <t>1776903570.96</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>50764557.16</v>
+        <v>44201426.71</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,17 +6800,17 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6870,17 +6870,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>16854.118</t>
+          <t>16934.062</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.07</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>946394875.2</t>
+          <t>1030169557.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>2163437979.1</t>
+          <t>1957468999.34</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>61794246.37</v>
+        <v>50764557.16</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,17 +7231,17 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>52365.835</t>
+          <t>16854.118</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,62 +7489,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>54.85</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-133.56</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>955349345.2</t>
+          <t>946394875.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>721647627.7</t>
+          <t>771003853.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>2402549153.18</t>
+          <t>2163437979.1</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>233701717</t>
+          <t>175391021</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-144174153.2400175</t>
+          <t>-112486707.1454632</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>76961261.38</v>
+        <v>61794246.37</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,17 +7727,17 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7426.262</t>
+          <t>52365.835</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-24.74</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>50.98</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>59.29</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>54.73</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-136.12</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>381782819.0</t>
+          <t>2715531091.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>505140710.2</t>
+          <t>955349345.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>501963719.2</t>
+          <t>721647627.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2548936714.28</t>
+          <t>2402549153.18</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3176991</t>
+          <t>233701717</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-184380592.2611023</t>
+          <t>-144174153.2400175</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-102649650.64</v>
+        <v>76961261.38</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,17 +8093,17 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="CD18" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6580.167</t>
+          <t>7426.262</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>-6.16</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-30.37</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>50.98</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>59.59</t>
+          <t>59.29</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-136.69</t>
+          <t>-136.12</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>313260581.0</t>
+          <t>381782819.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>531114807.2</t>
+          <t>505140710.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>511080645.4</t>
+          <t>501963719.2</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2772797348.26</t>
+          <t>2548936714.28</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>20034161</t>
+          <t>3176991</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-199240763.4657515</t>
+          <t>-184380592.2611023</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-105526151.13</v>
+        <v>-102649650.64</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>17.21</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,17 +8524,17 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9726.752</t>
+          <t>6580.167</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-29.93</t>
+          <t>-30.37</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8782,62 +8782,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-14.3</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>59.59</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-136.15</t>
+          <t>-136.69</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>458810419.0</t>
+          <t>313260581.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>583628887.2</t>
+          <t>531114807.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>529295603.5</t>
+          <t>511080645.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>2895834496.86</t>
+          <t>2772797348.26</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>54333283</t>
+          <t>20034161</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-216279783.8905731</t>
+          <t>-199240763.4657515</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-98524978.08</v>
+        <v>-105526151.13</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>17.21</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>18985.299</t>
+          <t>9726.752</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-29.63</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9213,62 +9213,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-13.94</t>
+          <t>-14.3</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>51.78</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>54.31</t>
+          <t>54.43</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-135.73</t>
+          <t>-136.15</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>907361816.0</t>
+          <t>458810419.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>595612832.4</t>
+          <t>583628887.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>525692219.6</t>
+          <t>529295603.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>2953848981.62</t>
+          <t>2895834496.86</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>69920612</t>
+          <t>54333283</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-237689748.5834216</t>
+          <t>-216279783.8905731</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-100599178.58</v>
+        <v>-98524978.08</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.96</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
+          <t>46.8</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
           <t>47.3</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>47.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>9234.129</t>
+          <t>18985.299</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-29.63</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,17 +9629,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-13.94</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>50.58</t>
+          <t>49.98</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>52.26</t>
+          <t>51.78</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>60.42</t>
+          <t>60.17</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>54.19</t>
+          <t>54.31</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-135.56</t>
+          <t>-135.73</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>464487916.0</t>
+          <t>907361816.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>487945910.2</t>
+          <t>595612832.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>469310663.0</t>
+          <t>525692219.6</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>3055293723.54</t>
+          <t>2953848981.62</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>18635247</t>
+          <t>69920612</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-262615306.766223</t>
+          <t>-237689748.5834216</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-148028572.59</v>
+        <v>-100599178.58</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10271.075</t>
+          <t>9234.129</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-25.48</t>
+          <t>-24.89</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-12.86</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.58</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>52.26</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>60.63</t>
+          <t>60.42</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>54.03</t>
+          <t>54.19</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-135.86</t>
+          <t>-135.56</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>511653304.0</t>
+          <t>464487916.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>498786728.2</t>
+          <t>487945910.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>463094155.0</t>
+          <t>469310663.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>3237534067.52</t>
+          <t>3055293723.54</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>35692573</t>
+          <t>18635247</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-283449258.4345579</t>
+          <t>-262615306.766223</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-163047340.02</v>
+        <v>-148028572.59</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/數位內容.xlsx
+++ b/Result/checksun_type/數位內容.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,14 +1014,14 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF2" t="inlineStr">
         <is>
           <t>27.27</t>
@@ -1029,62 +1029,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-37.40</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>129.6</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>152.7</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-6.82908030781107</t>
+          <t>-6.357929395098112</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>5.373577389639848</t>
+          <t>-3.766599375176838</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1272,17 +1272,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,147 +1450,147 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>18.43</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-47.71</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-107.24</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>1749.258468335788</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>231.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>129.6</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>109.4</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>153.1</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-6.82908030781107</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>5.373577389639848</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>231</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>18.99</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-59.68</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-106.38</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>1751.798672566372</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>112.6</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>104.6</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>149.36</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-9.047745343711238</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-4.582369281680613</t>
-        </is>
-      </c>
-      <c r="BD3" t="n">
-        <v>127</v>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG3" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1713,17 +1713,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
           <t>18.99</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>112.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>149.36</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-7.498637052078394</t>
+          <t>-4.582369281680613</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
+          <t>18.99</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
           <t>19.01</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>19.02</t>
-        </is>
-      </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>147.56</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-5.504068257929575</t>
+          <t>-7.498637052078394</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>196</v>
+        <v>72</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>145.88</t>
+          <t>147.56</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-15.74382468564805</t>
+          <t>-5.504068257929575</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>22</v>
+        <v>196</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,37 +3194,37 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>149.38</t>
+          <t>145.88</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-11.1669115579013</t>
+          <t>-15.74382468564805</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.61</t>
+          <t>-104.37</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>148.46</t>
+          <t>149.38</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-10.17221628922797</t>
+          <t>-10.32524633056233</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-17.51536024833804</t>
+          <t>-11.1669115579013</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>26</v>
+        <v>146</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -4066,14 +4066,14 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF9" t="inlineStr">
         <is>
           <t>100.0</t>
@@ -4081,64 +4081,64 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>19.03</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>19.05</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.82</t>
+          <t>-104.61</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>149.84</t>
+          <t>148.46</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-8.837099205753413</t>
+          <t>-10.17221628922797</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-13.10188122580702</t>
+          <t>-17.51536024833804</t>
         </is>
       </c>
       <c r="BD9" t="n">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-6.76</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,47 +4502,47 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -4557,17 +4557,17 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-19.28</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,22 +4592,22 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -4617,21 +4617,21 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8.061684293016393</t>
+          <t>-8.837099205753413</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-6.328986864126762</t>
+          <t>-13.10188122580702</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,102 +4832,102 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>-5.92</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-2.23</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-15.45</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>19.65</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
           <t>-5.07</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-04-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-0.53</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>-5.07</t>
-        </is>
-      </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,72 +4938,72 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>58.31</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-43.17</t>
+          <t>-19.28</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.62</t>
+          <t>-104.85</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>111.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>148.52</t>
+          <t>149.84</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-8.376720189178144</t>
+          <t>-8.061684293016393</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-5.748816816578966</t>
+          <t>-6.328986864126762</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,79 +5374,79 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>58.31</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>18.38</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-43.17</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>18.32</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>19.09</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-72.00</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-104.62</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>123.9</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>146.46</t>
+          <t>148.52</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8.854520802377994</t>
+          <t>-8.376720189178144</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-7.071830433775744</t>
+          <t>-5.748816816578966</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.77</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>56.17</t>
+          <t>55.78</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>664802561.8</t>
+          <t>549695262.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>1482928219.1</t>
+          <t>1388106125.2</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>429086972</v>
+        <v>302147334</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>56.17</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>751503060.6</t>
+          <t>664802561.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>1565117969.24</t>
+          <t>1482928219.1</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>476122067</v>
+        <v>429086972</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,17 +6439,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>50.18</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>1199384865.4</t>
+          <t>751503060.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>1647059956.98</t>
+          <t>1565117969.24</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>17580088.42918277</t>
+          <t>-13116137.5801748</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>631079227</v>
+        <v>476122067</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>50.38</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>57.56</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>1149525583.8</t>
+          <t>1199384865.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>1776903570.96</t>
+          <t>1647059956.98</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>44201426.71293712</t>
+          <t>17580088.42918277</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>910040711</v>
+        <v>631079227</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-7.32</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,67 +7554,67 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>58.07</t>
+          <t>57.56</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>1030169557.8</t>
+          <t>1149525583.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>1957468999.34</t>
+          <t>1776903570.96</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>50764557.16426682</t>
+          <t>44201426.71293712</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>877683832</v>
+        <v>910040711</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,17 +7747,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7817,17 +7817,17 @@
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16854.118</t>
+          <t>16934.062</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-7.66</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.07</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>946394875.2</t>
+          <t>1030169557.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2163437979.1</t>
+          <t>1957468999.34</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>61794246.37458563</t>
+          <t>50764557.16426682</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>862589466</v>
+        <v>877683832</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,17 +8183,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52365.835</t>
+          <t>16854.118</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,62 +8441,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>54.85</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-133.56</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>955349345.2</t>
+          <t>946394875.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>721647627.7</t>
+          <t>771003853.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2402549153.18</t>
+          <t>2163437979.1</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>233701717</t>
+          <t>175391021</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-144174153.2400175</t>
+          <t>-112486707.1454632</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>76961261.37594843</t>
+          <t>61794246.37458563</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>2715531091</v>
+        <v>862589466</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,17 +8684,17 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7426.262</t>
+          <t>52365.835</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-24.74</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>50.98</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>59.29</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>54.73</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-136.12</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>381782819.0</t>
+          <t>2715531091.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>505140710.2</t>
+          <t>955349345.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>501963719.2</t>
+          <t>721647627.7</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>2548936714.28</t>
+          <t>2402549153.18</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>3176991</t>
+          <t>233701717</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-184380592.2611023</t>
+          <t>-144174153.2400175</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-102649650.6355312</t>
+          <t>76961261.37594843</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>381782819</v>
+        <v>2715531091</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,17 +9055,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6580.167</t>
+          <t>7426.262</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>-8.5</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-30.37</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>50.98</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>59.59</t>
+          <t>59.29</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-136.69</t>
+          <t>-136.12</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>313260581.0</t>
+          <t>381782819.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>531114807.2</t>
+          <t>505140710.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>511080645.4</t>
+          <t>501963719.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>2772797348.26</t>
+          <t>2548936714.28</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>20034161</t>
+          <t>3176991</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-199240763.4657515</t>
+          <t>-184380592.2611023</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-105526151.1292332</t>
+          <t>-102649650.6355312</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>313260581</v>
+        <v>381782819</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>17.21</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,17 +9491,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>9726.752</t>
+          <t>6580.167</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-29.93</t>
+          <t>-30.37</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9749,62 +9749,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-14.3</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>59.59</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-136.15</t>
+          <t>-136.69</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>458810419.0</t>
+          <t>313260581.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>583628887.2</t>
+          <t>531114807.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>529295603.5</t>
+          <t>511080645.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>2895834496.86</t>
+          <t>2772797348.26</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>54333283</t>
+          <t>20034161</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-216279783.8905731</t>
+          <t>-199240763.4657515</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-98524978.07990623</t>
+          <t>-105526151.1292332</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>458810419</v>
+        <v>313260581</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>17.21</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>18985.299</t>
+          <t>9726.752</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-29.63</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10185,62 +10185,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-13.94</t>
+          <t>-14.3</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>51.78</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>54.31</t>
+          <t>54.43</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-135.73</t>
+          <t>-136.15</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>907361816.0</t>
+          <t>458810419.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>595612832.4</t>
+          <t>583628887.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>525692219.6</t>
+          <t>529295603.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>2953848981.62</t>
+          <t>2895834496.86</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>69920612</t>
+          <t>54333283</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-237689748.5834216</t>
+          <t>-216279783.8905731</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-100599178.5780139</t>
+          <t>-98524978.07990623</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>907361816</v>
+        <v>458810419</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.96</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
+          <t>46.8</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
           <t>47.3</t>
-        </is>
-      </c>
-      <c r="CG23" t="inlineStr">
-        <is>
-          <t>47.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/數位內容.xlsx
+++ b/Result/checksun_type/數位內容.xlsx
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1029,132 +1029,132 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>18.32</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-28.65</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-108.61</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>1746.727941176471</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>152.68</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-6.917564584493647</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-9.995558126169087</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-37.40</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-107.99</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>1749.258468335788</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>128.8</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>97.7</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>152.7</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-6.357929395098112</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-3.766599375176838</t>
-        </is>
-      </c>
-      <c r="BD2" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG2" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1465,62 +1465,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-37.40</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1749.258468335788</t>
+          <t>1746.727941176471</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>129.6</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>152.7</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-6.82908030781107</t>
+          <t>-6.357929395098112</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>5.373577389639848</t>
+          <t>-3.766599375176838</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1708,17 +1708,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,7 +1886,7 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1896,137 +1896,137 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>18.43</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-47.71</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-107.24</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>1746.727941176471</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>231.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>129.6</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>109.4</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>153.1</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-6.82908030781107</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>5.373577389639848</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>231</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>18.99</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-59.68</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-106.38</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>1749.258468335788</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>112.6</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>104.6</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>149.36</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-9.047745343711238</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-4.582369281680613</t>
-        </is>
-      </c>
-      <c r="BD4" t="n">
-        <v>127</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG4" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,7 +2322,7 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -2332,67 +2332,67 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
           <t>18.99</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1749.258468335788</t>
+          <t>1746.727941176471</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>112.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>149.36</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-7.498637052078394</t>
+          <t>-4.582369281680613</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,7 +2758,7 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2768,67 +2768,67 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
+          <t>18.99</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
           <t>19.01</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>19.02</t>
-        </is>
-      </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1749.258468335788</t>
+          <t>1746.727941176471</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>147.56</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-5.504068257929575</t>
+          <t>-7.498637052078394</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>196</v>
+        <v>72</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,7 +3194,7 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -3204,67 +3204,67 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1749.258468335788</t>
+          <t>1746.727941176471</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>145.88</t>
+          <t>147.56</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-15.74382468564805</t>
+          <t>-5.504068257929575</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>22</v>
+        <v>196</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,7 +3630,7 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -3640,27 +3640,27 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3670,12 +3670,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -3690,17 +3690,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1749.258468335788</t>
+          <t>1746.727941176471</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>149.38</t>
+          <t>145.88</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-11.1669115579013</t>
+          <t>-15.74382468564805</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,7 +4066,7 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -4076,67 +4076,67 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.61</t>
+          <t>-104.37</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1749.258468335788</t>
+          <t>1746.727941176471</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>148.46</t>
+          <t>149.38</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-10.17221628922797</t>
+          <t>-10.32524633056233</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-17.51536024833804</t>
+          <t>-11.1669115579013</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>26</v>
+        <v>146</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -4502,7 +4502,7 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -4517,64 +4517,64 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>19.03</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>19.05</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.82</t>
+          <t>-104.61</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1749.258468335788</t>
+          <t>1746.727941176471</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -4602,32 +4602,32 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>149.84</t>
+          <t>148.46</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8.837099205753413</t>
+          <t>-10.17221628922797</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-13.10188122580702</t>
+          <t>-17.51536024833804</t>
         </is>
       </c>
       <c r="BD10" t="n">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-6.76</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,7 +4938,7 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -4948,37 +4948,37 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -4993,17 +4993,17 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-19.28</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,22 +5028,22 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1749.258468335788</t>
+          <t>1746.727941176471</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
@@ -5053,21 +5053,21 @@
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-8.061684293016393</t>
+          <t>-8.837099205753413</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-6.328986864126762</t>
+          <t>-13.10188122580702</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,102 +5268,102 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>-5.92</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-3.75</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-15.45</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>19.65</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
           <t>-5.07</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-2.23</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-04-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>-0.53</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>-5.07</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,7 +5374,7 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -5384,62 +5384,62 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>58.31</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-43.17</t>
+          <t>-19.28</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.62</t>
+          <t>-104.85</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1749.258468335788</t>
+          <t>1746.727941176471</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>111.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>148.52</t>
+          <t>149.84</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8.376720189178144</t>
+          <t>-8.061684293016393</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-5.748816816578966</t>
+          <t>-6.328986864126762</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>49.77</t>
+          <t>49.57</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>55.78</t>
+          <t>55.39</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>549695262.2</t>
+          <t>427404646.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>1388106125.2</t>
+          <t>1336844077.5</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>302147334</v>
+        <v>298587633</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.77</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>56.17</t>
+          <t>55.78</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>664802561.8</t>
+          <t>549695262.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>1482928219.1</t>
+          <t>1388106125.2</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>429086972</v>
+        <v>302147334</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>56.17</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>751503060.6</t>
+          <t>664802561.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>1565117969.24</t>
+          <t>1482928219.1</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>476122067</v>
+        <v>429086972</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,17 +6875,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>50.18</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>1199384865.4</t>
+          <t>751503060.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>1647059956.98</t>
+          <t>1565117969.24</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>17580088.42918277</t>
+          <t>-13116137.5801748</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>631079227</v>
+        <v>476122067</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>50.38</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>57.56</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>1149525583.8</t>
+          <t>1199384865.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>1776903570.96</t>
+          <t>1647059956.98</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>44201426.71293712</t>
+          <t>17580088.42918277</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>910040711</v>
+        <v>631079227</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-7.66</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,67 +7990,67 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>58.07</t>
+          <t>57.56</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1030169557.8</t>
+          <t>1149525583.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>1957468999.34</t>
+          <t>1776903570.96</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>50764557.16426682</t>
+          <t>44201426.71293712</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>877683832</v>
+        <v>910040711</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,17 +8183,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8253,17 +8253,17 @@
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16854.118</t>
+          <t>16934.062</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>-6.1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.07</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>946394875.2</t>
+          <t>1030169557.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2163437979.1</t>
+          <t>1957468999.34</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>61794246.37458563</t>
+          <t>50764557.16426682</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>862589466</v>
+        <v>877683832</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,17 +8619,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52365.835</t>
+          <t>16854.118</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,62 +8877,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>54.85</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-133.56</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>955349345.2</t>
+          <t>946394875.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>721647627.7</t>
+          <t>771003853.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>2402549153.18</t>
+          <t>2163437979.1</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>233701717</t>
+          <t>175391021</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-144174153.2400175</t>
+          <t>-112486707.1454632</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>76961261.37594843</t>
+          <t>61794246.37458563</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>2715531091</v>
+        <v>862589466</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,17 +9120,17 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7426.262</t>
+          <t>52365.835</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-8.5</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-24.74</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>50.98</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>59.29</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>54.73</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-136.12</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>381782819.0</t>
+          <t>2715531091.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>505140710.2</t>
+          <t>955349345.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>501963719.2</t>
+          <t>721647627.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>2548936714.28</t>
+          <t>2402549153.18</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>3176991</t>
+          <t>233701717</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-184380592.2611023</t>
+          <t>-144174153.2400175</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-102649650.6355312</t>
+          <t>76961261.37594843</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>381782819</v>
+        <v>2715531091</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,97 +9446,97 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
+          <t>26.68</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>宏達電</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>宏達電</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>-36.86822403006653</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>-14.58459224643812</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>-2.04560003730758</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>7.01</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
+          <t>35.20%</t>
+        </is>
+      </c>
+      <c r="BX21" t="inlineStr">
+        <is>
+          <t>-119.21%</t>
+        </is>
+      </c>
+      <c r="BY21" t="inlineStr">
+        <is>
           <t>28.93</t>
         </is>
       </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>宏達電</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>宏達電</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>-36.86822403006653</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>-14.58459224643812</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>-2.04560003730758</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="BT21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU21" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="BV21" t="inlineStr">
-        <is>
-          <t>6.91</t>
-        </is>
-      </c>
-      <c r="BW21" t="inlineStr">
-        <is>
-          <t>35.20%</t>
-        </is>
-      </c>
-      <c r="BX21" t="inlineStr">
-        <is>
-          <t>-119.21%</t>
-        </is>
-      </c>
-      <c r="BY21" t="inlineStr">
-        <is>
-          <t>28.44</t>
-        </is>
-      </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>6580.167</t>
+          <t>7426.262</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-30.37</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>50.98</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>59.59</t>
+          <t>59.29</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-136.69</t>
+          <t>-136.12</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>313260581.0</t>
+          <t>381782819.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>531114807.2</t>
+          <t>505140710.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>511080645.4</t>
+          <t>501963719.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>2772797348.26</t>
+          <t>2548936714.28</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>20034161</t>
+          <t>3176991</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-199240763.4657515</t>
+          <t>-184380592.2611023</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-105526151.1292332</t>
+          <t>-102649650.6355312</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>313260581</v>
+        <v>381782819</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>17.21</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9726.752</t>
+          <t>6580.167</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-29.93</t>
+          <t>-30.37</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10185,62 +10185,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-14.3</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>59.59</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-136.15</t>
+          <t>-136.69</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>458810419.0</t>
+          <t>313260581.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>583628887.2</t>
+          <t>531114807.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>529295603.5</t>
+          <t>511080645.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>2895834496.86</t>
+          <t>2772797348.26</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>54333283</t>
+          <t>20034161</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-216279783.8905731</t>
+          <t>-199240763.4657515</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-98524978.07990623</t>
+          <t>-105526151.1292332</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>458810419</v>
+        <v>313260581</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>17.21</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/數位內容.xlsx
+++ b/Result/checksun_type/數位內容.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>17.75</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18.32</t>
+          <t>18.24</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-109.42</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1746.727941176471</t>
+          <t>1744.76872246696</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>152.68</t>
+          <t>150.4</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-6.917564584493647</t>
+          <t>-5.069622386680692</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-9.995558126169087</t>
+          <t>5.094059701290561</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>19</v>
+        <v>275</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1450,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1465,132 +1465,132 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>18.32</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-28.65</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-108.61</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>1744.76872246696</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>152.68</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-6.917564584493647</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-9.995558126169087</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-37.40</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-107.99</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>1746.727941176471</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>128.8</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>97.7</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>152.7</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-6.357929395098112</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-3.766599375176838</t>
-        </is>
-      </c>
-      <c r="BD3" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG3" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1901,62 +1901,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-37.40</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1746.727941176471</t>
+          <t>1744.76872246696</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>129.6</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>152.7</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-6.82908030781107</t>
+          <t>-6.357929395098112</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>5.373577389639848</t>
+          <t>-3.766599375176838</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,17 +2144,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,147 +2322,147 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>18.43</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-47.71</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-107.24</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>1744.76872246696</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>231.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>129.6</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>109.4</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>153.1</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-6.82908030781107</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>5.373577389639848</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>231</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>18.99</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-59.68</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-106.38</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>1746.727941176471</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>112.6</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>104.6</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>149.36</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-9.047745343711238</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-4.582369281680613</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>127</v>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG5" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
           <t>18.99</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1746.727941176471</t>
+          <t>1744.76872246696</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>112.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>149.36</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-7.498637052078394</t>
+          <t>-4.582369281680613</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
+          <t>18.99</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
           <t>19.01</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>19.02</t>
-        </is>
-      </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1746.727941176471</t>
+          <t>1744.76872246696</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>147.56</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-5.504068257929575</t>
+          <t>-7.498637052078394</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>196</v>
+        <v>72</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1746.727941176471</t>
+          <t>1744.76872246696</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>145.88</t>
+          <t>147.56</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-15.74382468564805</t>
+          <t>-5.504068257929575</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>22</v>
+        <v>196</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,37 +4066,37 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1746.727941176471</t>
+          <t>1744.76872246696</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>149.38</t>
+          <t>145.88</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-11.1669115579013</t>
+          <t>-15.74382468564805</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-9.94</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.61</t>
+          <t>-104.37</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1746.727941176471</t>
+          <t>1744.76872246696</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>148.46</t>
+          <t>149.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-10.17221628922797</t>
+          <t>-10.32524633056233</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-17.51536024833804</t>
+          <t>-11.1669115579013</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>26</v>
+        <v>146</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,64 +4953,64 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>19.03</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>19.05</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.82</t>
+          <t>-104.61</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1746.727941176471</t>
+          <t>1744.76872246696</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -5038,32 +5038,32 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>149.84</t>
+          <t>148.46</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-8.837099205753413</t>
+          <t>-10.17221628922797</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-13.10188122580702</t>
+          <t>-17.51536024833804</t>
         </is>
       </c>
       <c r="BD11" t="n">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,47 +5374,47 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -5429,17 +5429,17 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-19.28</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,22 +5464,22 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1746.727941176471</t>
+          <t>1744.76872246696</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -5489,21 +5489,21 @@
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8.061684293016393</t>
+          <t>-8.837099205753413</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-6.328986864126762</t>
+          <t>-13.10188122580702</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6182.1</t>
+          <t>5896.567</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-45.79</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>49.46</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>55.04</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.71</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-126.20</t>
+          <t>-125.39</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>427404646.6</t>
+          <t>359053739.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>788465115.2</t>
+          <t>779219302.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>1336844077.5</t>
+          <t>1233289107.3</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-361060468</t>
+          <t>-420165562</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-53779413.22102299</t>
+          <t>-59484245.83182855</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-80434512.81531477</t>
+          <t>-90860825.19125909</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>298587633</v>
+        <v>289324693</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>49.77</t>
+          <t>49.57</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>55.78</t>
+          <t>55.39</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>549695262.2</t>
+          <t>427404646.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>1388106125.2</t>
+          <t>1336844077.5</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>302147334</v>
+        <v>298587633</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.77</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>56.17</t>
+          <t>55.78</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>664802561.8</t>
+          <t>549695262.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>1482928219.1</t>
+          <t>1388106125.2</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>429086972</v>
+        <v>302147334</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,102 +7012,102 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-17.48</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-01-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>41.8</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>48.05</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>-29.19</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>-13.01</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>5.15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
           <t>-0.72</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-11.94</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-07-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-01-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-02-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>67.5</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>48.05</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>-27.85</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>-13.01</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>5.54</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>-3.08</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>56.17</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>751503060.6</t>
+          <t>664802561.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>1565117969.24</t>
+          <t>1482928219.1</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>476122067</v>
+        <v>429086972</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,17 +7311,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>50.18</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>1199384865.4</t>
+          <t>751503060.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>1647059956.98</t>
+          <t>1565117969.24</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>17580088.42918277</t>
+          <t>-13116137.5801748</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>631079227</v>
+        <v>476122067</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>50.38</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>57.56</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1149525583.8</t>
+          <t>1199384865.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>1776903570.96</t>
+          <t>1647059956.98</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>44201426.71293712</t>
+          <t>17580088.42918277</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>910040711</v>
+        <v>631079227</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-6.1</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,67 +8426,67 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>58.07</t>
+          <t>57.56</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1030169557.8</t>
+          <t>1149525583.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>1957468999.34</t>
+          <t>1776903570.96</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>50764557.16426682</t>
+          <t>44201426.71293712</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>877683832</v>
+        <v>910040711</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,17 +8619,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8689,17 +8689,17 @@
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>16854.118</t>
+          <t>16934.062</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.07</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>946394875.2</t>
+          <t>1030169557.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>2163437979.1</t>
+          <t>1957468999.34</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>61794246.37458563</t>
+          <t>50764557.16426682</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>862589466</v>
+        <v>877683832</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,17 +9055,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>52365.835</t>
+          <t>16854.118</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9313,62 +9313,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>54.85</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-133.56</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>955349345.2</t>
+          <t>946394875.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>721647627.7</t>
+          <t>771003853.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>2402549153.18</t>
+          <t>2163437979.1</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>233701717</t>
+          <t>175391021</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-144174153.2400175</t>
+          <t>-112486707.1454632</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>76961261.37594843</t>
+          <t>61794246.37458563</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>2715531091</v>
+        <v>862589466</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,17 +9556,17 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7426.262</t>
+          <t>52365.835</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-24.74</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>50.98</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>59.29</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>54.73</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-136.12</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>381782819.0</t>
+          <t>2715531091.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>505140710.2</t>
+          <t>955349345.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>501963719.2</t>
+          <t>721647627.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>2548936714.28</t>
+          <t>2402549153.18</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>3176991</t>
+          <t>233701717</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-184380592.2611023</t>
+          <t>-144174153.2400175</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-102649650.6355312</t>
+          <t>76961261.37594843</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>381782819</v>
+        <v>2715531091</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6580.167</t>
+          <t>7426.262</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-5.3</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-30.37</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>50.98</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>59.59</t>
+          <t>59.29</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-136.69</t>
+          <t>-136.12</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>313260581.0</t>
+          <t>381782819.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>531114807.2</t>
+          <t>505140710.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>511080645.4</t>
+          <t>501963719.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>2772797348.26</t>
+          <t>2548936714.28</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>20034161</t>
+          <t>3176991</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-199240763.4657515</t>
+          <t>-184380592.2611023</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-105526151.1292332</t>
+          <t>-102649650.6355312</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>313260581</v>
+        <v>381782819</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>17.21</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/數位內容.xlsx
+++ b/Result/checksun_type/數位內容.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>17.53</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>18.24</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>18.83</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>18.83</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>275.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>134</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>113.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>150.4</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>150.4</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>5.094059701290561</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>275</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>275.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>17.7</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>18.32</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>18.87</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>18.87</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>19.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>93.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>93.40000000000001</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>88.3</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>152.68</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>152.68</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-9.995558126169087</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>19</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>17.61</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>18.37</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>18.37</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>18.9</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>18.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>128.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>128.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>97.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>152.7</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>152.7</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-3.766599375176838</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>18</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>17.77</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>18.43</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>18.93</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>18.93</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>231.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>129.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>129.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>109.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>153.1</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>153.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>5.373577389639848</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>231</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>231.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>17.98</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>18.52</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>18.95</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>127.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>112.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>112.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>104.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>149.36</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>149.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-4.582369281680613</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>127</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>18.31</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>18.64</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>18.99</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>18.99</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>92.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>92.40000000000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>97.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>147.2</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>147.2</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-7.498637052078394</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>72</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>18.51</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>18.74</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>19.01</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>196.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>83.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>83.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>97.4</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>147.56</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>147.56</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-5.504068257929575</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>196</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,21 +4067,17 @@
           <t>18.81</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AM9" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>19.04</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
       <c r="AP9" t="inlineStr">
         <is>
           <t>12.53</t>
@@ -4164,20 +4118,16 @@
           <t>22.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>66.59999999999999</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>98.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>145.88</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>145.88</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-15.74382468564805</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>22</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,21 +4497,17 @@
           <t>18.83</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>18.92</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AM10" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="AO10" t="inlineStr">
         <is>
           <t>19.04</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
       <c r="AP10" t="inlineStr">
         <is>
           <t>21.95</t>
@@ -4600,20 +4548,16 @@
           <t>146.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>89.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>105.7</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>149.38</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>149.38</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-11.1669115579013</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>146</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>18.78</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>18.96</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>19.03</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>26.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>96.59999999999999</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>109.6</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>148.46</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>148.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-17.51536024833804</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>26</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>18.66</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>19.03</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>26.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>103.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>103.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>112.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>149.84</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>149.84</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-13.10188122580702</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>26</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>48.32</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>49.46</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>55.04</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>55.04</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>289324693.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>359053739.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>359053739.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>779219302.6</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1233289107.3</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1233289107.3</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-90860825.19125909</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>289324693</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>289324693.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>48.31</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>49.57</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>55.39</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>55.39</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>298587633.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>427404646.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>427404646.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>788465115.2</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1336844077.5</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1336844077.5</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-80434512.81531477</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>298587633</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>298587633.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>48.41</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>49.77</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>55.78</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>55.78</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>302147334.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>549695262.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>549695262.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>789932410.0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1388106125.2</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1388106125.2</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-63659577.53484738</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>302147334</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>302147334.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>49.14</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>56.17</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>56.17</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>429086972.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>664802561.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>664802561.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>805598718.5</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1482928219.1</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1482928219.1</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-37803224.47222078</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>429086972</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>429086972.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>49.73999999999999</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>50.18</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>56.62</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>56.62</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>476122067.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>751503060.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>751503060.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>853426202.9</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1565117969.24</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1565117969.24</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-13116137.5801748</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>476122067</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>476122067.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>50.16</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>50.38</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>57.1</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>50.38</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>57.1</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>631079227.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>1199384865.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>1199384865.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>852262787.8</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1647059956.98</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1647059956.98</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>17580088.42918277</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>631079227</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>631079227.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>50.69</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>50.56</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>57.56</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>50.56</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>57.56</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>910040711.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>1149525583.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>1149525583.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>840320195.5</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1776903570.96</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1776903570.96</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>44201426.71293712</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>910040711</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>910040711.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>50.32</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>50.72</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>58.07</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>58.07</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>877683832.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>1030169557.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>1030169557.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>806899222.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1957468999.34</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1957468999.34</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>50764557.16426682</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>877683832</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>877683832.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>49.52</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>50.73</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>58.46</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>50.73</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>58.46</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>862589466.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>946394875.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>946394875.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>771003853.8</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>2163437979.1</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>2163437979.1</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>61794246.37458563</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>862589466</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>862589466.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>48.86</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>50.84</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>58.9</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>2715531091.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>955349345.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>955349345.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>721647627.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>2402549153.18</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>2402549153.18</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>76961261.37594843</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>2715531091</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>2715531091.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>48.84</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>50.98</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>59.29</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>50.98</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>59.29</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>381782819.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>505140710.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>505140710.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>501963719.2</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>2548936714.28</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>2548936714.28</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-102649650.6355312</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>381782819</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>381782819.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/數位內容.xlsx
+++ b/Result/checksun_type/數位內容.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-8.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>18.24</v>
+        <v>18.16</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.83</v>
+        <v>18.79</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-34.40</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-109.42</t>
+          <t>-110.21</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>150.4</v>
+        <v>145.48</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-5.069622386680692</t>
+          <t>-4.877458836732884</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>5.094059701290561</t>
+          <t>-3.820559312019938</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>18.32</v>
+        <v>18.24</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.87</v>
+        <v>18.83</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-109.42</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>93.40000000000001</v>
+        <v>134</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>152.68</v>
+        <v>150.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-6.917564584493647</t>
+          <t>-5.069622386680692</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-9.995558126169087</t>
+          <t>5.094059701290561</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1874,14 +1874,14 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF4" t="inlineStr">
         <is>
           <t>27.27</t>
@@ -1889,126 +1889,126 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>18.37</v>
+        <v>18.32</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.9</v>
+        <v>18.87</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-28.65</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-108.61</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>1742.24780058651</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>152.68</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-6.917564584493647</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-9.995558126169087</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-37.40</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-107.99</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>1744.76872246696</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>97.7</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-6.357929395098112</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-3.766599375176838</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG4" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,14 +2304,14 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF5" t="inlineStr">
         <is>
           <t>27.27</t>
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>18.43</v>
+        <v>18.37</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.93</v>
+        <v>18.9</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-37.40</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>129.6</v>
+        <v>128.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>153.1</v>
+        <v>152.7</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-6.82908030781107</t>
+          <t>-6.357929395098112</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>5.373577389639848</t>
+          <t>-3.766599375176838</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>18.52</v>
+        <v>18.43</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.95</v>
+        <v>18.93</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-59.68</t>
+          <t>-47.71</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.38</t>
+          <t>-107.24</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>112.6</v>
+        <v>129.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>104.6</t>
+          <t>109.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>149.36</v>
+        <v>153.1</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-9.047745343711238</t>
+          <t>-6.82908030781107</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-4.582369281680613</t>
+          <t>5.373577389639848</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.64</v>
+        <v>18.52</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.99</v>
+        <v>18.95</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>92.40000000000001</v>
+        <v>112.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>147.2</v>
+        <v>149.36</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-7.498637052078394</t>
+          <t>-4.582369281680613</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>18.74</v>
+        <v>18.64</v>
       </c>
       <c r="AN8" t="n">
-        <v>19.01</v>
+        <v>18.99</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>83.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>147.56</v>
+        <v>147.2</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-5.504068257929575</t>
+          <t>-7.498637052078394</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.86</v>
+        <v>18.74</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.04</v>
+        <v>19.01</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>66.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>145.88</v>
+        <v>147.56</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-15.74382468564805</t>
+          <t>-5.504068257929575</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,37 +4454,37 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4494,11 +4494,11 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.92</v>
+        <v>18.86</v>
       </c>
       <c r="AN10" t="n">
         <v>19.04</v>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>89.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>149.38</v>
+        <v>145.88</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-11.1669115579013</t>
+          <t>-15.74382468564805</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.96</v>
+        <v>18.92</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.03</v>
+        <v>19.04</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.61</t>
+          <t>-104.37</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>96.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>148.46</v>
+        <v>149.38</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-10.17221628922797</t>
+          <t>-10.32524633056233</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-17.51536024833804</t>
+          <t>-11.1669115579013</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -5314,14 +5314,14 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF12" t="inlineStr">
         <is>
           <t>100.0</t>
@@ -5329,60 +5329,60 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.98</v>
+        <v>18.96</v>
       </c>
       <c r="AN12" t="n">
         <v>19.03</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.82</t>
+          <t>-104.61</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -5409,29 +5409,29 @@
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>103.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>149.84</v>
+        <v>148.46</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8.837099205753413</t>
+          <t>-10.17221628922797</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-13.10188122580702</t>
+          <t>-17.51536024833804</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5896.567</t>
+          <t>4211.204</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-42.23</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,58 +5759,58 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="AN13" t="n">
-        <v>55.04</v>
+        <v>54.69</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>55.71</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-125.39</t>
+          <t>-124.40</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>359053739.8</v>
+        <v>305206453</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>779219302.6</t>
+          <t>528354756.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>1233289107.3</v>
+        <v>1193416018.88</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-420165562</t>
+          <t>-223148303</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-59484245.83182855</t>
+          <t>-66036000.73841473</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-90860825.19125909</t>
+          <t>-102070652.7246387</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5996,17 +5996,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6182.1</t>
+          <t>5896.567</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-45.79</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>49.57</v>
+        <v>49.46</v>
       </c>
       <c r="AN14" t="n">
-        <v>55.39</v>
+        <v>55.04</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.71</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-126.20</t>
+          <t>-125.39</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>427404646.6</v>
+        <v>359053739.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>788465115.2</t>
+          <t>779219302.6</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>1336844077.5</v>
+        <v>1233289107.3</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-361060468</t>
+          <t>-420165562</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-53779413.22102299</t>
+          <t>-59484245.83182855</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-80434512.81531477</t>
+          <t>-90860825.19125909</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>49.77</v>
+        <v>49.57</v>
       </c>
       <c r="AN15" t="n">
-        <v>55.78</v>
+        <v>55.39</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>549695262.2</v>
+        <v>427404646.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>1388106125.2</v>
+        <v>1336844077.5</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>50</v>
+        <v>49.77</v>
       </c>
       <c r="AN16" t="n">
-        <v>56.17</v>
+        <v>55.78</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>664802561.8</v>
+        <v>549695262.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>1482928219.1</v>
+        <v>1388106125.2</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>50.18</v>
+        <v>50</v>
       </c>
       <c r="AN17" t="n">
-        <v>56.62</v>
+        <v>56.17</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>751503060.6</v>
+        <v>664802561.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>1565117969.24</v>
+        <v>1482928219.1</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>50.38</v>
+        <v>50.18</v>
       </c>
       <c r="AN18" t="n">
-        <v>57.1</v>
+        <v>56.62</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>1199384865.4</v>
+        <v>751503060.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>1647059956.98</v>
+        <v>1565117969.24</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>17580088.42918277</t>
+          <t>-13116137.5801748</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>50.56</v>
+        <v>50.38</v>
       </c>
       <c r="AN19" t="n">
-        <v>57.56</v>
+        <v>57.1</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>1149525583.8</v>
+        <v>1199384865.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>1776903570.96</v>
+        <v>1647059956.98</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>44201426.71293712</t>
+          <t>17580088.42918277</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,63 +8754,63 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>50.72</v>
+        <v>50.56</v>
       </c>
       <c r="AN20" t="n">
-        <v>58.07</v>
+        <v>57.56</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>1030169557.8</v>
+        <v>1149525583.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>1957468999.34</v>
+        <v>1776903570.96</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>50764557.16426682</t>
+          <t>44201426.71293712</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>16854.118</t>
+          <t>16934.062</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>50.73</v>
+        <v>50.72</v>
       </c>
       <c r="AN21" t="n">
-        <v>58.46</v>
+        <v>58.07</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>946394875.2</v>
+        <v>1030169557.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>2163437979.1</v>
+        <v>1957468999.34</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>61794246.37458563</t>
+          <t>50764557.16426682</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,17 +9371,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>52365.835</t>
+          <t>16854.118</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,12 +9513,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>50.84</v>
+        <v>50.73</v>
       </c>
       <c r="AN22" t="n">
-        <v>58.9</v>
+        <v>58.46</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>54.85</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-133.56</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>955349345.2</v>
+        <v>946394875.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>721647627.7</t>
+          <t>771003853.8</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>2402549153.18</v>
+        <v>2163437979.1</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>233701717</t>
+          <t>175391021</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-144174153.2400175</t>
+          <t>-112486707.1454632</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>76961261.37594843</t>
+          <t>61794246.37458563</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9866,17 +9866,17 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7426.262</t>
+          <t>52365.835</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.3</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-24.74</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>50.98</v>
+        <v>50.84</v>
       </c>
       <c r="AN23" t="n">
-        <v>59.29</v>
+        <v>58.9</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>54.73</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-136.12</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>381782819.0</t>
+          <t>2715531091.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>505140710.2</v>
+        <v>955349345.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>501963719.2</t>
+          <t>721647627.7</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>2548936714.28</v>
+        <v>2402549153.18</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>3176991</t>
+          <t>233701717</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-184380592.2611023</t>
+          <t>-144174153.2400175</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-102649650.6355312</t>
+          <t>76961261.37594843</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>381782819.0</t>
+          <t>2715531091.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/數位內容.xlsx
+++ b/Result/checksun_type/數位內容.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.00</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>18.16</v>
+        <v>18.07</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.79</v>
+        <v>18.74</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.29</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-110.21</t>
+          <t>-111.08</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>112</v>
+        <v>110.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>145.48</v>
+        <v>146.4</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4.877458836732884</t>
+          <t>-3.260200344702716</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-3.820559312019938</t>
+          <t>5.634721361463207</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-8.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>18.24</v>
+        <v>18.16</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.83</v>
+        <v>18.79</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-34.40</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-109.42</t>
+          <t>-110.21</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>150.4</v>
+        <v>145.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-5.069622386680692</t>
+          <t>-4.877458836732884</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>5.094059701290561</t>
+          <t>-3.820559312019938</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>18.32</v>
+        <v>18.24</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.87</v>
+        <v>18.83</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-109.42</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>93.40000000000001</v>
+        <v>134</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>152.68</v>
+        <v>150.4</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-6.917564584493647</t>
+          <t>-5.069622386680692</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-9.995558126169087</t>
+          <t>5.094059701290561</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,126 +2319,126 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>18.37</v>
+        <v>18.32</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.9</v>
+        <v>18.87</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-28.65</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-108.61</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>1740.191068814056</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>152.68</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-6.917564584493647</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-9.995558126169087</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-37.40</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-107.99</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>1742.24780058651</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>97.7</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-6.357929395098112</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-3.766599375176838</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG5" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>18.43</v>
+        <v>18.37</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.93</v>
+        <v>18.9</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-37.40</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>129.6</v>
+        <v>128.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>153.1</v>
+        <v>152.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-6.82908030781107</t>
+          <t>-6.357929395098112</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>5.373577389639848</t>
+          <t>-3.766599375176838</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.52</v>
+        <v>18.43</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.95</v>
+        <v>18.93</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-59.68</t>
+          <t>-47.71</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.38</t>
+          <t>-107.24</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>112.6</v>
+        <v>129.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>104.6</t>
+          <t>109.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>149.36</v>
+        <v>153.1</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-9.047745343711238</t>
+          <t>-6.82908030781107</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-4.582369281680613</t>
+          <t>5.373577389639848</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>18.64</v>
+        <v>18.52</v>
       </c>
       <c r="AN8" t="n">
-        <v>18.99</v>
+        <v>18.95</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>92.40000000000001</v>
+        <v>112.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>147.2</v>
+        <v>149.36</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-7.498637052078394</t>
+          <t>-4.582369281680613</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-5.9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.74</v>
+        <v>18.64</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.01</v>
+        <v>18.99</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>83.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>147.56</v>
+        <v>147.2</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-5.504068257929575</t>
+          <t>-7.498637052078394</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.86</v>
+        <v>18.74</v>
       </c>
       <c r="AN10" t="n">
-        <v>19.04</v>
+        <v>19.01</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>66.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>145.88</v>
+        <v>147.56</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-15.74382468564805</t>
+          <t>-5.504068257929575</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-9.44</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,37 +4884,37 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4924,11 +4924,11 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.92</v>
+        <v>18.86</v>
       </c>
       <c r="AN11" t="n">
         <v>19.04</v>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>89.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>149.38</v>
+        <v>145.88</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-11.1669115579013</t>
+          <t>-15.74382468564805</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.96</v>
+        <v>18.92</v>
       </c>
       <c r="AN12" t="n">
-        <v>19.03</v>
+        <v>19.04</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.61</t>
+          <t>-104.37</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>96.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>148.46</v>
+        <v>149.38</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-10.17221628922797</t>
+          <t>-10.32524633056233</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-17.51536024833804</t>
+          <t>-11.1669115579013</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,42 +5613,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6085.789</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>4211.204</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-42.23</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-26.00</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>59.82</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-9.3</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>49.4</v>
+        <v>49.37</v>
       </c>
       <c r="AN13" t="n">
-        <v>54.69</v>
+        <v>54.43</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-124.40</t>
+          <t>-123.12</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>305206453</v>
+        <v>279791428.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>528354756.8</t>
+          <t>472296995.2</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>1193416018.88</v>
+        <v>1139949931.8</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-223148303</t>
+          <t>-192505566</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-66036000.73841473</t>
+          <t>-71296815.91787222</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-102070652.7246387</t>
+          <t>-100231299.4048884</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5896.567</t>
+          <t>4211.204</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-42.23</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,58 +6189,58 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="AN14" t="n">
-        <v>55.04</v>
+        <v>54.69</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>55.71</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-125.39</t>
+          <t>-124.40</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>359053739.8</v>
+        <v>305206453</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>779219302.6</t>
+          <t>528354756.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>1233289107.3</v>
+        <v>1193416018.88</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-420165562</t>
+          <t>-223148303</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-59484245.83182855</t>
+          <t>-66036000.73841473</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-90860825.19125909</t>
+          <t>-102070652.7246387</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,17 +6426,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6182.1</t>
+          <t>5896.567</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-45.79</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>49.57</v>
+        <v>49.46</v>
       </c>
       <c r="AN15" t="n">
-        <v>55.39</v>
+        <v>55.04</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.71</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-126.20</t>
+          <t>-125.39</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>427404646.6</v>
+        <v>359053739.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>788465115.2</t>
+          <t>779219302.6</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>1336844077.5</v>
+        <v>1233289107.3</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-361060468</t>
+          <t>-420165562</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-53779413.22102299</t>
+          <t>-59484245.83182855</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-80434512.81531477</t>
+          <t>-90860825.19125909</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>49.77</v>
+        <v>49.57</v>
       </c>
       <c r="AN16" t="n">
-        <v>55.78</v>
+        <v>55.39</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>549695262.2</v>
+        <v>427404646.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>1388106125.2</v>
+        <v>1336844077.5</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>50</v>
+        <v>49.77</v>
       </c>
       <c r="AN17" t="n">
-        <v>56.17</v>
+        <v>55.78</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>664802561.8</v>
+        <v>549695262.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>1482928219.1</v>
+        <v>1388106125.2</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>50.18</v>
+        <v>50</v>
       </c>
       <c r="AN18" t="n">
-        <v>56.62</v>
+        <v>56.17</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>751503060.6</v>
+        <v>664802561.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>1565117969.24</v>
+        <v>1482928219.1</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>50.38</v>
+        <v>50.18</v>
       </c>
       <c r="AN19" t="n">
-        <v>57.1</v>
+        <v>56.62</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>1199384865.4</v>
+        <v>751503060.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>1647059956.98</v>
+        <v>1565117969.24</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>17580088.42918277</t>
+          <t>-13116137.5801748</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>50.56</v>
+        <v>50.38</v>
       </c>
       <c r="AN20" t="n">
-        <v>57.56</v>
+        <v>57.1</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>1149525583.8</v>
+        <v>1199384865.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>1776903570.96</v>
+        <v>1647059956.98</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>44201426.71293712</t>
+          <t>17580088.42918277</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,12 +8941,12 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,63 +9184,63 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>50.72</v>
+        <v>50.56</v>
       </c>
       <c r="AN21" t="n">
-        <v>58.07</v>
+        <v>57.56</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>1030169557.8</v>
+        <v>1149525583.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>1957468999.34</v>
+        <v>1776903570.96</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>50764557.16426682</t>
+          <t>44201426.71293712</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9441,17 +9441,17 @@
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>16854.118</t>
+          <t>16934.062</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>50.73</v>
+        <v>50.72</v>
       </c>
       <c r="AN22" t="n">
-        <v>58.46</v>
+        <v>58.07</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>946394875.2</v>
+        <v>1030169557.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>2163437979.1</v>
+        <v>1957468999.34</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>61794246.37458563</t>
+          <t>50764557.16426682</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>52365.835</t>
+          <t>16854.118</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>50.84</v>
+        <v>50.73</v>
       </c>
       <c r="AN23" t="n">
-        <v>58.9</v>
+        <v>58.46</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>54.85</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-133.56</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>955349345.2</v>
+        <v>946394875.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>721647627.7</t>
+          <t>771003853.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>2402549153.18</v>
+        <v>2163437979.1</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>233701717</t>
+          <t>175391021</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-144174153.2400175</t>
+          <t>-112486707.1454632</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>76961261.37594843</t>
+          <t>61794246.37458563</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,17 +10296,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/數位內容.xlsx
+++ b/Result/checksun_type/數位內容.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>18.07</v>
+        <v>17.98</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.74</v>
+        <v>18.69</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-31.29</t>
+          <t>-35.21</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-111.08</t>
+          <t>-112.15</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>110.8</v>
+        <v>124</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>126.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>146.4</v>
+        <v>146.22</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3.260200344702716</t>
+          <t>-2.522084938000019</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>5.634721361463207</t>
+          <t>1.537549798864816</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-12.93</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.00</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>18.16</v>
+        <v>18.07</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.79</v>
+        <v>18.74</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.29</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-110.21</t>
+          <t>-111.08</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>112</v>
+        <v>110.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>145.48</v>
+        <v>146.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4.877458836732884</t>
+          <t>-3.260200344702716</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-3.820559312019938</t>
+          <t>5.634721361463207</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-8.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>18.24</v>
+        <v>18.16</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.83</v>
+        <v>18.79</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-34.40</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-109.42</t>
+          <t>-110.21</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>150.4</v>
+        <v>145.48</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-5.069622386680692</t>
+          <t>-4.877458836732884</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>5.094059701290561</t>
+          <t>-3.820559312019938</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>18.32</v>
+        <v>18.24</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.87</v>
+        <v>18.83</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-109.42</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>93.40000000000001</v>
+        <v>134</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>152.68</v>
+        <v>150.4</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-6.917564584493647</t>
+          <t>-5.069622386680692</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-9.995558126169087</t>
+          <t>5.094059701290561</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-7.58</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,126 +2749,126 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>18.37</v>
+        <v>18.32</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.9</v>
+        <v>18.87</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-28.65</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-108.61</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>1737.831140350877</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>152.68</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-6.917564584493647</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-9.995558126169087</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-37.40</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-107.99</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>1740.191068814056</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>97.7</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-6.357929395098112</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-3.766599375176838</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG6" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-7.58</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,58 +3179,58 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.43</v>
+        <v>18.37</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.93</v>
+        <v>18.9</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-37.40</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>129.6</v>
+        <v>128.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>153.1</v>
+        <v>152.7</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-6.82908030781107</t>
+          <t>-6.357929395098112</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>5.373577389639848</t>
+          <t>-3.766599375176838</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,17 +3416,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-7.58</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>18.52</v>
+        <v>18.43</v>
       </c>
       <c r="AN8" t="n">
-        <v>18.95</v>
+        <v>18.93</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-59.68</t>
+          <t>-47.71</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.38</t>
+          <t>-107.24</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>112.6</v>
+        <v>129.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>104.6</t>
+          <t>109.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>149.36</v>
+        <v>153.1</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-9.047745343711238</t>
+          <t>-6.82908030781107</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-4.582369281680613</t>
+          <t>5.373577389639848</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.64</v>
+        <v>18.52</v>
       </c>
       <c r="AN9" t="n">
-        <v>18.99</v>
+        <v>18.95</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>92.40000000000001</v>
+        <v>112.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>147.2</v>
+        <v>149.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-7.498637052078394</t>
+          <t>-4.582369281680613</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-8.79</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.74</v>
+        <v>18.64</v>
       </c>
       <c r="AN10" t="n">
-        <v>19.01</v>
+        <v>18.99</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>83.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>147.56</v>
+        <v>147.2</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-5.504068257929575</t>
+          <t>-7.498637052078394</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9.44</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.86</v>
+        <v>18.74</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.04</v>
+        <v>19.01</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>66.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>145.88</v>
+        <v>147.56</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-15.74382468564805</t>
+          <t>-5.504068257929575</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-12.42</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,37 +5314,37 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5354,11 +5354,11 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.92</v>
+        <v>18.86</v>
       </c>
       <c r="AN12" t="n">
         <v>19.04</v>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>89.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>149.38</v>
+        <v>145.88</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-11.1669115579013</t>
+          <t>-15.74382468564805</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6085.789</t>
+          <t>6477.386</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-31.98</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-26.00</t>
+          <t>-27.48</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>59.82</t>
+          <t>65.42</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-9.3</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>49.37</v>
+        <v>49.23</v>
       </c>
       <c r="AN13" t="n">
-        <v>54.43</v>
+        <v>54.08</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>56.01</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-123.12</t>
+          <t>-121.89</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>279791428.6</v>
+        <v>283316111.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>472296995.2</t>
+          <t>416505686.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>1139949931.8</v>
+        <v>1087982910.56</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-192505566</t>
+          <t>-133189575</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-71296815.91787222</t>
+          <t>-74959775.3529597</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-100231299.4048884</t>
+          <t>-95106052.24594092</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
           <t>48.95</t>
-        </is>
-      </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>49.95</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4211.204</t>
+          <t>6085.789</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-42.23</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-26.00</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>59.82</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-9.3</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>49.4</v>
+        <v>49.37</v>
       </c>
       <c r="AN14" t="n">
-        <v>54.69</v>
+        <v>54.43</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-124.40</t>
+          <t>-123.12</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>305206453</v>
+        <v>279791428.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>528354756.8</t>
+          <t>472296995.2</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>1193416018.88</v>
+        <v>1139949931.8</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-223148303</t>
+          <t>-192505566</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-66036000.73841473</t>
+          <t>-71296815.91787222</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-102070652.7246387</t>
+          <t>-100231299.4048884</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5896.567</t>
+          <t>4211.204</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-42.23</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,12 +6604,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,58 +6619,58 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="AN15" t="n">
-        <v>55.04</v>
+        <v>54.69</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>55.71</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-125.39</t>
+          <t>-124.40</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>359053739.8</v>
+        <v>305206453</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>779219302.6</t>
+          <t>528354756.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>1233289107.3</v>
+        <v>1193416018.88</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-420165562</t>
+          <t>-223148303</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-59484245.83182855</t>
+          <t>-66036000.73841473</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-90860825.19125909</t>
+          <t>-102070652.7246387</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,17 +6856,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6182.1</t>
+          <t>5896.567</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-45.79</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>49.57</v>
+        <v>49.46</v>
       </c>
       <c r="AN16" t="n">
-        <v>55.39</v>
+        <v>55.04</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.71</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-126.20</t>
+          <t>-125.39</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>427404646.6</v>
+        <v>359053739.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>788465115.2</t>
+          <t>779219302.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>1336844077.5</v>
+        <v>1233289107.3</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-361060468</t>
+          <t>-420165562</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-53779413.22102299</t>
+          <t>-59484245.83182855</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-80434512.81531477</t>
+          <t>-90860825.19125909</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>49.77</v>
+        <v>49.57</v>
       </c>
       <c r="AN17" t="n">
-        <v>55.78</v>
+        <v>55.39</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>549695262.2</v>
+        <v>427404646.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>1388106125.2</v>
+        <v>1336844077.5</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>50</v>
+        <v>49.77</v>
       </c>
       <c r="AN18" t="n">
-        <v>56.17</v>
+        <v>55.78</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>664802561.8</v>
+        <v>549695262.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>1482928219.1</v>
+        <v>1388106125.2</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>50.18</v>
+        <v>50</v>
       </c>
       <c r="AN19" t="n">
-        <v>56.62</v>
+        <v>56.17</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>751503060.6</v>
+        <v>664802561.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>1565117969.24</v>
+        <v>1482928219.1</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>50.38</v>
+        <v>50.18</v>
       </c>
       <c r="AN20" t="n">
-        <v>57.1</v>
+        <v>56.62</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>1199384865.4</v>
+        <v>751503060.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>1647059956.98</v>
+        <v>1565117969.24</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>17580088.42918277</t>
+          <t>-13116137.5801748</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>50.56</v>
+        <v>50.38</v>
       </c>
       <c r="AN21" t="n">
-        <v>57.56</v>
+        <v>57.1</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>1149525583.8</v>
+        <v>1199384865.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>1776903570.96</v>
+        <v>1647059956.98</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>44201426.71293712</t>
+          <t>17580088.42918277</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,63 +9614,63 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>50.72</v>
+        <v>50.56</v>
       </c>
       <c r="AN22" t="n">
-        <v>58.07</v>
+        <v>57.56</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>1030169557.8</v>
+        <v>1149525583.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>1957468999.34</v>
+        <v>1776903570.96</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>50764557.16426682</t>
+          <t>44201426.71293712</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9871,17 +9871,17 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>16854.118</t>
+          <t>16934.062</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>50.73</v>
+        <v>50.72</v>
       </c>
       <c r="AN23" t="n">
-        <v>58.46</v>
+        <v>58.07</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>946394875.2</v>
+        <v>1030169557.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>2163437979.1</v>
+        <v>1957468999.34</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>61794246.37458563</t>
+          <t>50764557.16426682</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/數位內容.xlsx
+++ b/Result/checksun_type/數位內容.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.00</t>
+          <t>-10.40</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1024,63 +1024,63 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.98</v>
+        <v>17.92</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.69</v>
+        <v>18.64</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-35.21</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-112.15</t>
+          <t>-113.11</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1109,29 +1109,29 @@
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>126.4</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>146.22</v>
+        <v>146.36</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2.522084938000019</t>
+          <t>-2.344673261373195</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>1.537549798864816</t>
+          <t>-1.368909039925668</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>-11.35</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,7 +1444,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>18.07</v>
+        <v>17.98</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.74</v>
+        <v>18.69</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-31.29</t>
+          <t>-35.21</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-111.08</t>
+          <t>-112.15</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>110.8</v>
+        <v>124</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>126.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>146.4</v>
+        <v>146.22</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3.260200344702716</t>
+          <t>-2.522084938000019</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>5.634721361463207</t>
+          <t>1.537549798864816</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-12.93</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.00</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1884,63 +1884,63 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>18.16</v>
+        <v>18.07</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.79</v>
+        <v>18.74</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.29</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.21</t>
+          <t>-111.08</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>112</v>
+        <v>110.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>145.48</v>
+        <v>146.4</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-4.877458836732884</t>
+          <t>-3.260200344702716</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-3.820559312019938</t>
+          <t>5.634721361463207</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-8.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,7 +2304,7 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -2314,63 +2314,63 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>18.24</v>
+        <v>18.16</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.83</v>
+        <v>18.79</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-34.40</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-109.42</t>
+          <t>-110.21</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>150.4</v>
+        <v>145.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-5.069622386680692</t>
+          <t>-4.877458836732884</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>5.094059701290561</t>
+          <t>-3.820559312019938</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-7.58</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,7 +2734,7 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2744,63 +2744,63 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>18.32</v>
+        <v>18.24</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.87</v>
+        <v>18.83</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-109.42</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>93.40000000000001</v>
+        <v>134</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>152.68</v>
+        <v>150.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-6.917564584493647</t>
+          <t>-5.069622386680692</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-9.995558126169087</t>
+          <t>5.094059701290561</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.58</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -3164,7 +3164,7 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -3179,126 +3179,126 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.37</v>
+        <v>18.32</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.9</v>
+        <v>18.87</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-28.65</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-108.61</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>1735.478102189781</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>152.68</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-6.917564584493647</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-9.995558126169087</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-37.40</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-107.99</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>1737.831140350877</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>97.7</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-6.357929395098112</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-3.766599375176838</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG7" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-7.58</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,7 +3594,7 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>18.43</v>
+        <v>18.37</v>
       </c>
       <c r="AN8" t="n">
-        <v>18.93</v>
+        <v>18.9</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-37.40</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>129.6</v>
+        <v>128.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>153.1</v>
+        <v>152.7</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-6.82908030781107</t>
+          <t>-6.357929395098112</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>5.373577389639848</t>
+          <t>-3.766599375176838</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,7 +4024,7 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -4034,63 +4034,63 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.52</v>
+        <v>18.43</v>
       </c>
       <c r="AN9" t="n">
-        <v>18.95</v>
+        <v>18.93</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-59.68</t>
+          <t>-47.71</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-106.38</t>
+          <t>-107.24</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>112.6</v>
+        <v>129.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>104.6</t>
+          <t>109.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>149.36</v>
+        <v>153.1</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-9.047745343711238</t>
+          <t>-6.82908030781107</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-4.582369281680613</t>
+          <t>5.373577389639848</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.79</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,7 +4454,7 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -4464,63 +4464,63 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.64</v>
+        <v>18.52</v>
       </c>
       <c r="AN10" t="n">
-        <v>18.99</v>
+        <v>18.95</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>92.40000000000001</v>
+        <v>112.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>147.2</v>
+        <v>149.36</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-7.498637052078394</t>
+          <t>-4.582369281680613</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,7 +4884,7 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -4894,63 +4894,63 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.74</v>
+        <v>18.64</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.01</v>
+        <v>18.99</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>83.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>147.56</v>
+        <v>147.2</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-5.504068257929575</t>
+          <t>-7.498637052078394</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-12.42</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,7 +5314,7 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -5324,63 +5324,63 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.86</v>
+        <v>18.74</v>
       </c>
       <c r="AN12" t="n">
-        <v>19.04</v>
+        <v>19.01</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>66.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>145.88</v>
+        <v>147.56</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-15.74382468564805</t>
+          <t>-5.504068257929575</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6477.386</t>
+          <t>4440.277</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-31.98</t>
+          <t>-23.09</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-27.48</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>65.42</t>
+          <t>64.49</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-8.4</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>49.23</v>
+        <v>49.17</v>
       </c>
       <c r="AN13" t="n">
-        <v>54.08</v>
+        <v>53.68</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-121.89</t>
+          <t>-120.81</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>283316111.4</v>
+        <v>267060943</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>416505686.8</t>
+          <t>347232794.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>1087982910.56</v>
+        <v>1007913686.44</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-133189575</t>
+          <t>-80171851</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-74959775.3529597</t>
+          <t>-78323679.09920117</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-95106052.24594092</t>
+          <t>-96825149.70352924</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6085.789</t>
+          <t>6477.386</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-31.98</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-26.00</t>
+          <t>-27.48</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>59.82</t>
+          <t>65.42</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-9.3</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>49.37</v>
+        <v>49.23</v>
       </c>
       <c r="AN14" t="n">
-        <v>54.43</v>
+        <v>54.08</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>56.01</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-123.12</t>
+          <t>-121.89</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>279791428.6</v>
+        <v>283316111.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>472296995.2</t>
+          <t>416505686.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>1139949931.8</v>
+        <v>1087982910.56</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-192505566</t>
+          <t>-133189575</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-71296815.91787222</t>
+          <t>-74959775.3529597</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-100231299.4048884</t>
+          <t>-95106052.24594092</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
           <t>48.95</t>
-        </is>
-      </c>
-      <c r="CG14" t="inlineStr">
-        <is>
-          <t>49.95</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4211.204</t>
+          <t>6085.789</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-42.23</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-26.00</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>59.82</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-9.3</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>49.4</v>
+        <v>49.37</v>
       </c>
       <c r="AN15" t="n">
-        <v>54.69</v>
+        <v>54.43</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-124.40</t>
+          <t>-123.12</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>305206453</v>
+        <v>279791428.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>528354756.8</t>
+          <t>472296995.2</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>1193416018.88</v>
+        <v>1139949931.8</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-223148303</t>
+          <t>-192505566</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-66036000.73841473</t>
+          <t>-71296815.91787222</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-102070652.7246387</t>
+          <t>-100231299.4048884</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5896.567</t>
+          <t>4211.204</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-42.23</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,12 +7034,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7049,58 +7049,58 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="AN16" t="n">
-        <v>55.04</v>
+        <v>54.69</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>55.71</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-125.39</t>
+          <t>-124.40</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>359053739.8</v>
+        <v>305206453</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>779219302.6</t>
+          <t>528354756.8</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>1233289107.3</v>
+        <v>1193416018.88</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-420165562</t>
+          <t>-223148303</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-59484245.83182855</t>
+          <t>-66036000.73841473</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-90860825.19125909</t>
+          <t>-102070652.7246387</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,17 +7286,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6182.1</t>
+          <t>5896.567</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-45.79</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>49.57</v>
+        <v>49.46</v>
       </c>
       <c r="AN17" t="n">
-        <v>55.39</v>
+        <v>55.04</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-126.20</t>
+          <t>-125.39</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>427404646.6</v>
+        <v>359053739.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>788465115.2</t>
+          <t>779219302.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>1336844077.5</v>
+        <v>1233289107.3</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-361060468</t>
+          <t>-420165562</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-53779413.22102299</t>
+          <t>-59484245.83182855</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-80434512.81531477</t>
+          <t>-90860825.19125909</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>49.77</v>
+        <v>49.57</v>
       </c>
       <c r="AN18" t="n">
-        <v>55.78</v>
+        <v>55.39</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>549695262.2</v>
+        <v>427404646.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>1388106125.2</v>
+        <v>1336844077.5</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>50</v>
+        <v>49.77</v>
       </c>
       <c r="AN19" t="n">
-        <v>56.17</v>
+        <v>55.78</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>664802561.8</v>
+        <v>549695262.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>1482928219.1</v>
+        <v>1388106125.2</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>50.18</v>
+        <v>50</v>
       </c>
       <c r="AN20" t="n">
-        <v>56.62</v>
+        <v>56.17</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>751503060.6</v>
+        <v>664802561.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>1565117969.24</v>
+        <v>1482928219.1</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>50.38</v>
+        <v>50.18</v>
       </c>
       <c r="AN21" t="n">
-        <v>57.1</v>
+        <v>56.62</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>1199384865.4</v>
+        <v>751503060.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>1647059956.98</v>
+        <v>1565117969.24</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>17580088.42918277</t>
+          <t>-13116137.5801748</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,17 +9371,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>50.56</v>
+        <v>50.38</v>
       </c>
       <c r="AN22" t="n">
-        <v>57.56</v>
+        <v>57.1</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>1149525583.8</v>
+        <v>1199384865.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>1776903570.96</v>
+        <v>1647059956.98</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>44201426.71293712</t>
+          <t>17580088.42918277</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,63 +10044,63 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>50.72</v>
+        <v>50.56</v>
       </c>
       <c r="AN23" t="n">
-        <v>58.07</v>
+        <v>57.56</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>1030169557.8</v>
+        <v>1149525583.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>1957468999.34</v>
+        <v>1776903570.96</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>50764557.16426682</t>
+          <t>44201426.71293712</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/數位內容.xlsx
+++ b/Result/checksun_type/數位內容.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>-17.13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.40</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,63 +1014,63 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.92</v>
+        <v>17.84</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.64</v>
+        <v>18.59</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-22.01</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-113.11</t>
+          <t>-113.87</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>137</v>
+        <v>94.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>114.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>146.36</v>
+        <v>147.02</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2.344673261373195</t>
+          <t>-2.733063144405144</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1.368909039925668</t>
+          <t>-4.869207501080865</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-11.35</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-12.00</t>
+          <t>-10.40</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>17.98</v>
+        <v>17.92</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.69</v>
+        <v>18.64</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-35.21</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.15</t>
+          <t>-113.11</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1539,29 +1539,29 @@
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>126.4</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>146.22</v>
+        <v>146.36</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2.522084938000019</t>
+          <t>-2.344673261373195</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>1.537549798864816</t>
+          <t>-1.368909039925668</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>-11.35</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1894,53 +1894,53 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>18.07</v>
+        <v>17.98</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.74</v>
+        <v>18.69</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-31.29</t>
+          <t>-35.21</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-111.08</t>
+          <t>-112.15</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>110.8</v>
+        <v>124</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>126.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>146.4</v>
+        <v>146.22</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3.260200344702716</t>
+          <t>-2.522084938000019</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>5.634721361463207</t>
+          <t>1.537549798864816</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-12.93</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.00</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>18.16</v>
+        <v>18.07</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.79</v>
+        <v>18.74</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.29</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.21</t>
+          <t>-111.08</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>112</v>
+        <v>110.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>145.48</v>
+        <v>146.4</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-4.877458836732884</t>
+          <t>-3.260200344702716</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-3.820559312019938</t>
+          <t>5.634721361463207</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-8.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>18.24</v>
+        <v>18.16</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.83</v>
+        <v>18.79</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-34.40</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-109.42</t>
+          <t>-110.21</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>150.4</v>
+        <v>145.48</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-5.069622386680692</t>
+          <t>-4.877458836732884</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>5.094059701290561</t>
+          <t>-3.820559312019938</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.32</v>
+        <v>18.24</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.87</v>
+        <v>18.83</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-109.42</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>93.40000000000001</v>
+        <v>134</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>152.68</v>
+        <v>150.4</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-6.917564584493647</t>
+          <t>-5.069622386680692</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-9.995558126169087</t>
+          <t>5.094059701290561</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -3594,141 +3594,141 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>27.27</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>27.27</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>-3.37</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>-2.93</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>17.7</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-28.65</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-108.61</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>1733.088192419825</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>152.68</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>27.27</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>18.18</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0.80</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-4.12</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>-2.81</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>17.61</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
-        <v>18.37</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="AO8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-6.917564584493647</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-9.995558126169087</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
         <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-37.40</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-107.99</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>1735.478102189781</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>97.7</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-6.357929395098112</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-3.766599375176838</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG8" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.43</v>
+        <v>18.37</v>
       </c>
       <c r="AN9" t="n">
-        <v>18.93</v>
+        <v>18.9</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-37.40</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>129.6</v>
+        <v>128.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>153.1</v>
+        <v>152.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-6.82908030781107</t>
+          <t>-6.357929395098112</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>5.373577389639848</t>
+          <t>-3.766599375176838</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,17 +4276,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.52</v>
+        <v>18.43</v>
       </c>
       <c r="AN10" t="n">
-        <v>18.95</v>
+        <v>18.93</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-59.68</t>
+          <t>-47.71</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.38</t>
+          <t>-107.24</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>112.6</v>
+        <v>129.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>104.6</t>
+          <t>109.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>149.36</v>
+        <v>153.1</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-9.047745343711238</t>
+          <t>-6.82908030781107</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-4.582369281680613</t>
+          <t>5.373577389639848</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.64</v>
+        <v>18.52</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.99</v>
+        <v>18.95</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>92.40000000000001</v>
+        <v>112.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>147.2</v>
+        <v>149.36</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-7.498637052078394</t>
+          <t>-4.582369281680613</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.74</v>
+        <v>18.64</v>
       </c>
       <c r="AN12" t="n">
-        <v>19.01</v>
+        <v>18.99</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>83.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>147.56</v>
+        <v>147.2</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-5.504068257929575</t>
+          <t>-7.498637052078394</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d】;【x】看好</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4440.277</t>
+          <t>5508.131</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-23.09</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-27.04</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>64.49</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-8.4</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>49.17</v>
+        <v>49.12</v>
       </c>
       <c r="AN13" t="n">
-        <v>53.68</v>
+        <v>53.27</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-120.81</t>
+          <t>-119.67</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>267060943</v>
+        <v>263666319.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>347232794.8</t>
+          <t>311360029.6</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>1007913686.44</v>
+        <v>893391430.4</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-80171851</t>
+          <t>-47693710</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-78323679.09920117</t>
+          <t>-80347713.91182451</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-96825149.70352924</t>
+          <t>-91479905.38125283</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6477.386</t>
+          <t>4440.277</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-31.98</t>
+          <t>-23.09</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-27.48</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>65.42</t>
+          <t>64.49</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-8.4</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>49.23</v>
+        <v>49.17</v>
       </c>
       <c r="AN14" t="n">
-        <v>54.08</v>
+        <v>53.68</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-121.89</t>
+          <t>-120.81</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>283316111.4</v>
+        <v>267060943</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>416505686.8</t>
+          <t>347232794.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>1087982910.56</v>
+        <v>1007913686.44</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-133189575</t>
+          <t>-80171851</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-74959775.3529597</t>
+          <t>-78323679.09920117</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-95106052.24594092</t>
+          <t>-96825149.70352924</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6085.789</t>
+          <t>6477.386</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-31.98</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-26.00</t>
+          <t>-27.48</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>59.82</t>
+          <t>65.42</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-9.3</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>49.37</v>
+        <v>49.23</v>
       </c>
       <c r="AN15" t="n">
-        <v>54.43</v>
+        <v>54.08</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>56.01</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-123.12</t>
+          <t>-121.89</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>279791428.6</v>
+        <v>283316111.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>472296995.2</t>
+          <t>416505686.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>1139949931.8</v>
+        <v>1087982910.56</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-192505566</t>
+          <t>-133189575</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-71296815.91787222</t>
+          <t>-74959775.3529597</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-100231299.4048884</t>
+          <t>-95106052.24594092</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
           <t>48.95</t>
-        </is>
-      </c>
-      <c r="CG15" t="inlineStr">
-        <is>
-          <t>49.95</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,42 +6903,42 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6085.789</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>4211.204</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-1.24</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-42.23</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-26.00</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>59.82</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-9.3</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>49.4</v>
+        <v>49.37</v>
       </c>
       <c r="AN16" t="n">
-        <v>54.69</v>
+        <v>54.43</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-124.40</t>
+          <t>-123.12</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>305206453</v>
+        <v>279791428.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>528354756.8</t>
+          <t>472296995.2</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>1193416018.88</v>
+        <v>1139949931.8</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-223148303</t>
+          <t>-192505566</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-66036000.73841473</t>
+          <t>-71296815.91787222</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-102070652.7246387</t>
+          <t>-100231299.4048884</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5896.567</t>
+          <t>4211.204</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-42.23</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,12 +7464,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7479,58 +7479,58 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="AN17" t="n">
-        <v>55.04</v>
+        <v>54.69</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>55.71</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-125.39</t>
+          <t>-124.40</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>359053739.8</v>
+        <v>305206453</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>779219302.6</t>
+          <t>528354756.8</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>1233289107.3</v>
+        <v>1193416018.88</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-420165562</t>
+          <t>-223148303</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-59484245.83182855</t>
+          <t>-66036000.73841473</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-90860825.19125909</t>
+          <t>-102070652.7246387</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,17 +7716,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6182.1</t>
+          <t>5896.567</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-45.79</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>49.57</v>
+        <v>49.46</v>
       </c>
       <c r="AN18" t="n">
-        <v>55.39</v>
+        <v>55.04</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.71</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-126.20</t>
+          <t>-125.39</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>427404646.6</v>
+        <v>359053739.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>788465115.2</t>
+          <t>779219302.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>1336844077.5</v>
+        <v>1233289107.3</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-361060468</t>
+          <t>-420165562</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-53779413.22102299</t>
+          <t>-59484245.83182855</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-80434512.81531477</t>
+          <t>-90860825.19125909</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>49.77</v>
+        <v>49.57</v>
       </c>
       <c r="AN19" t="n">
-        <v>55.78</v>
+        <v>55.39</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>549695262.2</v>
+        <v>427404646.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>1388106125.2</v>
+        <v>1336844077.5</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>50</v>
+        <v>49.77</v>
       </c>
       <c r="AN20" t="n">
-        <v>56.17</v>
+        <v>55.78</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>664802561.8</v>
+        <v>549695262.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>1482928219.1</v>
+        <v>1388106125.2</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,12 +8941,12 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>50.18</v>
+        <v>50</v>
       </c>
       <c r="AN21" t="n">
-        <v>56.62</v>
+        <v>56.17</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>751503060.6</v>
+        <v>664802561.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>1565117969.24</v>
+        <v>1482928219.1</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,17 +9371,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>50.38</v>
+        <v>50.18</v>
       </c>
       <c r="AN22" t="n">
-        <v>57.1</v>
+        <v>56.62</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>1199384865.4</v>
+        <v>751503060.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>1647059956.98</v>
+        <v>1565117969.24</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>17580088.42918277</t>
+          <t>-13116137.5801748</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,102 +9938,102 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>40.73</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-01-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>41.8</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>48.05</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-27.33</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-13.01</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
           <t>-0.78</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>36.80</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-07-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-01-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-02-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>67.5</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>48.05</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>-27.63</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>-13.01</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10.58</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>-2.73</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>50.56</v>
+        <v>50.38</v>
       </c>
       <c r="AN23" t="n">
-        <v>57.56</v>
+        <v>57.1</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>1149525583.8</v>
+        <v>1199384865.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>1776903570.96</v>
+        <v>1647059956.98</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>44201426.71293712</t>
+          <t>17580088.42918277</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/數位內容.xlsx
+++ b/Result/checksun_type/數位內容.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-17.13</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,14 +1014,14 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF2" t="inlineStr">
         <is>
           <t>32.0</t>
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.84</v>
+        <v>17.77</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.59</v>
+        <v>18.54</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-22.01</t>
+          <t>-15.72</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-113.87</t>
+          <t>-114.44</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>114.4</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>147.02</v>
+        <v>146.98</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2.733063144405144</t>
+          <t>-3.950697466244736</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-4.869207501080865</t>
+          <t>-10.64768623636249</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>-17.13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.40</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,63 +1444,63 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>17.92</v>
+        <v>17.84</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.64</v>
+        <v>18.59</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-22.01</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-113.11</t>
+          <t>-113.87</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>137</v>
+        <v>94.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>114.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>146.36</v>
+        <v>147.02</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2.344673261373195</t>
+          <t>-2.733063144405144</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1.368909039925668</t>
+          <t>-4.869207501080865</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-11.35</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-12.00</t>
+          <t>-10.40</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>17.98</v>
+        <v>17.92</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.69</v>
+        <v>18.64</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-35.21</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.15</t>
+          <t>-113.11</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1969,29 +1969,29 @@
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>126.4</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>146.22</v>
+        <v>146.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2.522084938000019</t>
+          <t>-2.344673261373195</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1.537549798864816</t>
+          <t>-1.368909039925668</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>-11.35</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,14 +2304,14 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF5" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2324,53 +2324,53 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>18.07</v>
+        <v>17.98</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.74</v>
+        <v>18.69</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-31.29</t>
+          <t>-35.21</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-111.08</t>
+          <t>-112.15</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>110.8</v>
+        <v>124</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>126.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>146.4</v>
+        <v>146.22</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3.260200344702716</t>
+          <t>-2.522084938000019</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>5.634721361463207</t>
+          <t>1.537549798864816</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-12.93</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.00</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>18.16</v>
+        <v>18.07</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.79</v>
+        <v>18.74</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.29</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.21</t>
+          <t>-111.08</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>112</v>
+        <v>110.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>145.48</v>
+        <v>146.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-4.877458836732884</t>
+          <t>-3.260200344702716</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-3.820559312019938</t>
+          <t>5.634721361463207</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-8.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.24</v>
+        <v>18.16</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.83</v>
+        <v>18.79</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-34.40</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-109.42</t>
+          <t>-110.21</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>150.4</v>
+        <v>145.48</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-5.069622386680692</t>
+          <t>-4.877458836732884</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>5.094059701290561</t>
+          <t>-3.820559312019938</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>18.32</v>
+        <v>18.24</v>
       </c>
       <c r="AN8" t="n">
-        <v>18.87</v>
+        <v>18.83</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-109.42</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>93.40000000000001</v>
+        <v>134</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>152.68</v>
+        <v>150.4</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-6.917564584493647</t>
+          <t>-5.069622386680692</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-9.995558126169087</t>
+          <t>5.094059701290561</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3923,12 +3923,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -4024,14 +4024,14 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF9" t="inlineStr">
         <is>
           <t>27.27</t>
@@ -4039,126 +4039,126 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.37</v>
+        <v>18.32</v>
       </c>
       <c r="AN9" t="n">
-        <v>18.9</v>
+        <v>18.87</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-28.65</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-108.61</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>1730.60480349345</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>152.68</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-6.917564584493647</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-9.995558126169087</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-37.40</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-107.99</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>1733.088192419825</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>97.7</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-6.357929395098112</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-3.766599375176838</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG9" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,14 +4454,14 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF10" t="inlineStr">
         <is>
           <t>27.27</t>
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.43</v>
+        <v>18.37</v>
       </c>
       <c r="AN10" t="n">
-        <v>18.93</v>
+        <v>18.9</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-37.40</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>129.6</v>
+        <v>128.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>153.1</v>
+        <v>152.7</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-6.82908030781107</t>
+          <t>-6.357929395098112</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>5.373577389639848</t>
+          <t>-3.766599375176838</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.52</v>
+        <v>18.43</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.95</v>
+        <v>18.93</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-59.68</t>
+          <t>-47.71</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-106.38</t>
+          <t>-107.24</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>112.6</v>
+        <v>129.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>104.6</t>
+          <t>109.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>149.36</v>
+        <v>153.1</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-9.047745343711238</t>
+          <t>-6.82908030781107</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-4.582369281680613</t>
+          <t>5.373577389639848</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.64</v>
+        <v>18.52</v>
       </c>
       <c r="AN12" t="n">
-        <v>18.99</v>
+        <v>18.95</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>92.40000000000001</v>
+        <v>112.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>147.2</v>
+        <v>149.36</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-7.498637052078394</t>
+          <t>-4.582369281680613</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5508.131</t>
+          <t>8142.579</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-27.04</t>
+          <t>-27.11</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>49.12</v>
+        <v>49.04</v>
       </c>
       <c r="AN13" t="n">
-        <v>53.27</v>
+        <v>52.89</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-119.67</t>
+          <t>-118.51</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>263666319.4</v>
+        <v>303258012.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>311360029.6</t>
+          <t>304232232.7</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>893391430.4</v>
+        <v>833966853.42</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-47693710</t>
+          <t>-974220</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-80347713.91182451</t>
+          <t>-79604111.38633272</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-91479905.38125283</t>
+          <t>-75514297.49612796</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>22.69</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4440.277</t>
+          <t>5508.131</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-23.09</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-27.04</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>64.49</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-8.4</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>49.17</v>
+        <v>49.12</v>
       </c>
       <c r="AN14" t="n">
-        <v>53.68</v>
+        <v>53.27</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-120.81</t>
+          <t>-119.67</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>267060943</v>
+        <v>263666319.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>347232794.8</t>
+          <t>311360029.6</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>1007913686.44</v>
+        <v>893391430.4</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-80171851</t>
+          <t>-47693710</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-78323679.09920117</t>
+          <t>-80347713.91182451</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-96825149.70352924</t>
+          <t>-91479905.38125283</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6477.386</t>
+          <t>4440.277</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-31.98</t>
+          <t>-23.09</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-27.48</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>65.42</t>
+          <t>64.49</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-8.4</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>49.23</v>
+        <v>49.17</v>
       </c>
       <c r="AN15" t="n">
-        <v>54.08</v>
+        <v>53.68</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-121.89</t>
+          <t>-120.81</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>283316111.4</v>
+        <v>267060943</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>416505686.8</t>
+          <t>347232794.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>1087982910.56</v>
+        <v>1007913686.44</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-133189575</t>
+          <t>-80171851</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-74959775.3529597</t>
+          <t>-78323679.09920117</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-95106052.24594092</t>
+          <t>-96825149.70352924</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6085.789</t>
+          <t>6477.386</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-31.98</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-26.00</t>
+          <t>-27.48</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>59.82</t>
+          <t>65.42</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-9.3</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>49.37</v>
+        <v>49.23</v>
       </c>
       <c r="AN16" t="n">
-        <v>54.43</v>
+        <v>54.08</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>56.01</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-123.12</t>
+          <t>-121.89</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>279791428.6</v>
+        <v>283316111.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>472296995.2</t>
+          <t>416505686.8</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>1139949931.8</v>
+        <v>1087982910.56</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-192505566</t>
+          <t>-133189575</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-71296815.91787222</t>
+          <t>-74959775.3529597</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-100231299.4048884</t>
+          <t>-95106052.24594092</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
           <t>48.95</t>
-        </is>
-      </c>
-      <c r="CG16" t="inlineStr">
-        <is>
-          <t>49.95</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,42 +7333,42 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6085.789</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-1.52</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>4211.204</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-42.23</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-26.00</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>59.82</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-9.3</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>49.4</v>
+        <v>49.37</v>
       </c>
       <c r="AN17" t="n">
-        <v>54.69</v>
+        <v>54.43</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-124.40</t>
+          <t>-123.12</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>305206453</v>
+        <v>279791428.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>528354756.8</t>
+          <t>472296995.2</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>1193416018.88</v>
+        <v>1139949931.8</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-223148303</t>
+          <t>-192505566</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-66036000.73841473</t>
+          <t>-71296815.91787222</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-102070652.7246387</t>
+          <t>-100231299.4048884</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5896.567</t>
+          <t>4211.204</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-42.23</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,12 +7894,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7909,58 +7909,58 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="AN18" t="n">
-        <v>55.04</v>
+        <v>54.69</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>55.71</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-125.39</t>
+          <t>-124.40</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>359053739.8</v>
+        <v>305206453</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>779219302.6</t>
+          <t>528354756.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>1233289107.3</v>
+        <v>1193416018.88</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-420165562</t>
+          <t>-223148303</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-59484245.83182855</t>
+          <t>-66036000.73841473</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-90860825.19125909</t>
+          <t>-102070652.7246387</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,17 +8146,17 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6182.1</t>
+          <t>5896.567</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-45.79</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>49.57</v>
+        <v>49.46</v>
       </c>
       <c r="AN19" t="n">
-        <v>55.39</v>
+        <v>55.04</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.71</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-126.20</t>
+          <t>-125.39</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>427404646.6</v>
+        <v>359053739.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>788465115.2</t>
+          <t>779219302.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>1336844077.5</v>
+        <v>1233289107.3</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-361060468</t>
+          <t>-420165562</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-53779413.22102299</t>
+          <t>-59484245.83182855</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-80434512.81531477</t>
+          <t>-90860825.19125909</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>49.77</v>
+        <v>49.57</v>
       </c>
       <c r="AN20" t="n">
-        <v>55.78</v>
+        <v>55.39</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>549695262.2</v>
+        <v>427404646.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>1388106125.2</v>
+        <v>1336844077.5</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>50</v>
+        <v>49.77</v>
       </c>
       <c r="AN21" t="n">
-        <v>56.17</v>
+        <v>55.78</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>664802561.8</v>
+        <v>549695262.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>1482928219.1</v>
+        <v>1388106125.2</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>50.18</v>
+        <v>50</v>
       </c>
       <c r="AN22" t="n">
-        <v>56.62</v>
+        <v>56.17</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>751503060.6</v>
+        <v>664802561.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>1565117969.24</v>
+        <v>1482928219.1</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>50.38</v>
+        <v>50.18</v>
       </c>
       <c r="AN23" t="n">
-        <v>57.1</v>
+        <v>56.62</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>1199384865.4</v>
+        <v>751503060.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>1647059956.98</v>
+        <v>1565117969.24</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>17580088.42918277</t>
+          <t>-13116137.5801748</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/數位內容.xlsx
+++ b/Result/checksun_type/數位內容.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>17.45</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>16.9</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-19.78</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,69 +1019,61 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>29.33</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-5.42</t>
-        </is>
+          <t>46.67</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-4.56</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.77</v>
+        <v>17.72</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.54</v>
+        <v>18.51</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>18.71</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-15.72</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.53</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
+          <t>-2.90</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.46</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-114.44</t>
+          <t>-114.54</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1730.60480349345</t>
+          <t>1728.353197674419</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>95</v>
+        <v>74.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>146.98</v>
+        <v>146.54</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3.950697466244736</t>
+          <t>-4.373886962522906</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-10.64768623636249</t>
+          <t>-6.701429195048107</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,17 +1193,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>258</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,17 +1263,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-17.13</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,7 +1441,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,59 +1451,51 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>18.67</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-5.41</t>
-        </is>
+          <t>29.33</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-5.42</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>17.84</v>
+        <v>17.77</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.59</v>
+        <v>18.54</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-22.01</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.54</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.44</t>
-        </is>
+          <t>-15.72</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.46</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-113.87</t>
+          <t>-114.44</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1730.60480349345</t>
+          <t>1728.353197674419</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>114.4</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>147.02</v>
+        <v>146.98</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2.733063144405144</t>
+          <t>-3.950697465700142</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-4.869207501080865</t>
+          <t>-10.64768623624541</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,12 +1615,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>258</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1706,7 +1690,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>-17.13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.40</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,69 +1863,61 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-0.71</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-5.58</t>
-        </is>
+          <t>18.67</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-5.41</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>17.92</v>
+        <v>17.84</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.64</v>
+        <v>18.59</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-29.34</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.54</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.42</t>
-        </is>
+          <t>-22.01</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.44</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-113.11</t>
+          <t>-113.87</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1730.60480349345</t>
+          <t>1728.353197674419</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>137</v>
+        <v>94.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>114.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>146.36</v>
+        <v>147.02</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2.344673261373195</t>
+          <t>-2.733063143782822</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1.368909039925668</t>
+          <t>-4.869207500947056</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-11.35</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2037,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>258</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,7 +2149,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2188,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.00</t>
+          <t>-10.40</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,7 +2259,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2293,7 +2269,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,69 +2285,61 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-3.57</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-4.83</t>
-        </is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-5.58</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>17.98</v>
+        <v>17.92</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.69</v>
+        <v>18.64</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-35.21</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
+          <t>-29.34</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.42</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.15</t>
+          <t>-113.11</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,7 +2358,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1730.60480349345</t>
+          <t>1728.353197674419</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -2399,29 +2367,29 @@
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>126.4</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>146.22</v>
+        <v>146.36</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2.522084938000019</t>
+          <t>-2.344673260662052</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1.537549798864816</t>
+          <t>-1.368909039772745</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
@@ -2446,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>-11.35</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2459,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/